--- a/IMEA/planting_prog_mt.xlsx
+++ b/IMEA/planting_prog_mt.xlsx
@@ -1439,8 +1439,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1456,7 +1464,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1464,12 +1472,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1769,51 +1795,51 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44932</v>
       </c>
       <c r="B2" t="s">
@@ -1848,7 +1874,7 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44932</v>
       </c>
       <c r="B3" t="s">
@@ -1889,7 +1915,7 @@
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44932</v>
       </c>
       <c r="B4" t="s">
@@ -1930,7 +1956,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>44932</v>
       </c>
       <c r="B5" t="s">
@@ -1971,7 +1997,7 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>44932</v>
       </c>
       <c r="B6" t="s">
@@ -2012,7 +2038,7 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>44932</v>
       </c>
       <c r="B7" t="s">
@@ -2053,7 +2079,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>44932</v>
       </c>
       <c r="B8" t="s">
@@ -2094,7 +2120,7 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>44939</v>
       </c>
       <c r="B9" t="s">
@@ -2132,7 +2158,7 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>44939</v>
       </c>
       <c r="B10" t="s">
@@ -2176,7 +2202,7 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>44939</v>
       </c>
       <c r="B11" t="s">
@@ -2220,7 +2246,7 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>44939</v>
       </c>
       <c r="B12" t="s">
@@ -2264,7 +2290,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>44939</v>
       </c>
       <c r="B13" t="s">
@@ -2308,7 +2334,7 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>44939</v>
       </c>
       <c r="B14" t="s">
@@ -2352,7 +2378,7 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>44939</v>
       </c>
       <c r="B15" t="s">
@@ -2393,7 +2419,7 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>44946</v>
       </c>
       <c r="B16" t="s">
@@ -2431,7 +2457,7 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>44946</v>
       </c>
       <c r="B17" t="s">
@@ -2475,7 +2501,7 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>44946</v>
       </c>
       <c r="B18" t="s">
@@ -2519,7 +2545,7 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>44946</v>
       </c>
       <c r="B19" t="s">
@@ -2563,7 +2589,7 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>44946</v>
       </c>
       <c r="B20" t="s">
@@ -2607,7 +2633,7 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>44946</v>
       </c>
       <c r="B21" t="s">
@@ -2651,7 +2677,7 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>44946</v>
       </c>
       <c r="B22" t="s">
@@ -2695,7 +2721,7 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>44953</v>
       </c>
       <c r="B23" t="s">
@@ -2733,7 +2759,7 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>44953</v>
       </c>
       <c r="B24" t="s">
@@ -2777,7 +2803,7 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>44953</v>
       </c>
       <c r="B25" t="s">
@@ -2821,7 +2847,7 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>44953</v>
       </c>
       <c r="B26" t="s">
@@ -2865,7 +2891,7 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>44953</v>
       </c>
       <c r="B27" t="s">
@@ -2909,7 +2935,7 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>44953</v>
       </c>
       <c r="B28" t="s">
@@ -2953,7 +2979,7 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>44953</v>
       </c>
       <c r="B29" t="s">
@@ -2997,7 +3023,7 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>44960</v>
       </c>
       <c r="B30" t="s">
@@ -3035,7 +3061,7 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>44960</v>
       </c>
       <c r="B31" t="s">
@@ -3079,7 +3105,7 @@
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>44960</v>
       </c>
       <c r="B32" t="s">
@@ -3123,7 +3149,7 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>44960</v>
       </c>
       <c r="B33" t="s">
@@ -3167,7 +3193,7 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>44960</v>
       </c>
       <c r="B34" t="s">
@@ -3211,7 +3237,7 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>44960</v>
       </c>
       <c r="B35" t="s">
@@ -3255,7 +3281,7 @@
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>44960</v>
       </c>
       <c r="B36" t="s">
@@ -3299,7 +3325,7 @@
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>44967</v>
       </c>
       <c r="B37" t="s">
@@ -3337,7 +3363,7 @@
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>44967</v>
       </c>
       <c r="B38" t="s">
@@ -3381,7 +3407,7 @@
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>44967</v>
       </c>
       <c r="B39" t="s">
@@ -3425,7 +3451,7 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>44967</v>
       </c>
       <c r="B40" t="s">
@@ -3469,7 +3495,7 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>44967</v>
       </c>
       <c r="B41" t="s">
@@ -3513,7 +3539,7 @@
       </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>44967</v>
       </c>
       <c r="B42" t="s">
@@ -3557,7 +3583,7 @@
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>44967</v>
       </c>
       <c r="B43" t="s">
@@ -3601,7 +3627,7 @@
       </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>44974</v>
       </c>
       <c r="B44" t="s">
@@ -3639,7 +3665,7 @@
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>44974</v>
       </c>
       <c r="B45" t="s">
@@ -3683,7 +3709,7 @@
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>44974</v>
       </c>
       <c r="B46" t="s">
@@ -3727,7 +3753,7 @@
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>44974</v>
       </c>
       <c r="B47" t="s">
@@ -3771,7 +3797,7 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>44974</v>
       </c>
       <c r="B48" t="s">
@@ -3815,7 +3841,7 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>44974</v>
       </c>
       <c r="B49" t="s">
@@ -3859,7 +3885,7 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>44974</v>
       </c>
       <c r="B50" t="s">
@@ -3903,7 +3929,7 @@
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>44981</v>
       </c>
       <c r="B51" t="s">
@@ -3941,7 +3967,7 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>44981</v>
       </c>
       <c r="B52" t="s">
@@ -3985,7 +4011,7 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>44981</v>
       </c>
       <c r="B53" t="s">
@@ -4029,7 +4055,7 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>44981</v>
       </c>
       <c r="B54" t="s">
@@ -4073,7 +4099,7 @@
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>44981</v>
       </c>
       <c r="B55" t="s">
@@ -4117,7 +4143,7 @@
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>44981</v>
       </c>
       <c r="B56" t="s">
@@ -4161,7 +4187,7 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>44981</v>
       </c>
       <c r="B57" t="s">
@@ -4205,7 +4231,7 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>44988</v>
       </c>
       <c r="B58" t="s">
@@ -4243,7 +4269,7 @@
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>44988</v>
       </c>
       <c r="B59" t="s">
@@ -4287,7 +4313,7 @@
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>44988</v>
       </c>
       <c r="B60" t="s">
@@ -4331,7 +4357,7 @@
       </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>44988</v>
       </c>
       <c r="B61" t="s">
@@ -4375,7 +4401,7 @@
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>44988</v>
       </c>
       <c r="B62" t="s">
@@ -4419,7 +4445,7 @@
       </c>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>44988</v>
       </c>
       <c r="B63" t="s">
@@ -4463,7 +4489,7 @@
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>44988</v>
       </c>
       <c r="B64" t="s">
@@ -4507,7 +4533,7 @@
       </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>45268</v>
       </c>
       <c r="B65" t="s">
@@ -4545,7 +4571,7 @@
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>45268</v>
       </c>
       <c r="B66" t="s">
@@ -4589,7 +4615,7 @@
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>45275</v>
       </c>
       <c r="B67" t="s">
@@ -4627,7 +4653,7 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>45275</v>
       </c>
       <c r="B68" t="s">
@@ -4671,7 +4697,7 @@
       </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>45275</v>
       </c>
       <c r="B69" t="s">
@@ -4715,7 +4741,7 @@
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>45275</v>
       </c>
       <c r="B70" t="s">
@@ -4759,7 +4785,7 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>45275</v>
       </c>
       <c r="B71" t="s">
@@ -4803,7 +4829,7 @@
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>45282</v>
       </c>
       <c r="B72" t="s">
@@ -4841,7 +4867,7 @@
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>45282</v>
       </c>
       <c r="B73" t="s">
@@ -4885,7 +4911,7 @@
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>45282</v>
       </c>
       <c r="B74" t="s">
@@ -4929,7 +4955,7 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>45282</v>
       </c>
       <c r="B75" t="s">
@@ -4973,7 +4999,7 @@
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>45282</v>
       </c>
       <c r="B76" t="s">
@@ -5017,7 +5043,7 @@
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>45282</v>
       </c>
       <c r="B77" t="s">
@@ -5061,7 +5087,7 @@
       </c>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>45282</v>
       </c>
       <c r="B78" t="s">
@@ -5105,7 +5131,7 @@
       </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>45289</v>
       </c>
       <c r="B79" t="s">
@@ -5143,7 +5169,7 @@
       </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>45289</v>
       </c>
       <c r="B80" t="s">
@@ -5187,7 +5213,7 @@
       </c>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>45289</v>
       </c>
       <c r="B81" t="s">
@@ -5231,7 +5257,7 @@
       </c>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>45289</v>
       </c>
       <c r="B82" t="s">
@@ -5275,7 +5301,7 @@
       </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>45289</v>
       </c>
       <c r="B83" t="s">
@@ -5319,7 +5345,7 @@
       </c>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>45289</v>
       </c>
       <c r="B84" t="s">
@@ -5363,7 +5389,7 @@
       </c>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>45289</v>
       </c>
       <c r="B85" t="s">
@@ -5407,7 +5433,7 @@
       </c>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>45296</v>
       </c>
       <c r="B86" t="s">
@@ -5445,7 +5471,7 @@
       </c>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>45296</v>
       </c>
       <c r="B87" t="s">
@@ -5489,7 +5515,7 @@
       </c>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>45296</v>
       </c>
       <c r="B88" t="s">
@@ -5533,7 +5559,7 @@
       </c>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>45296</v>
       </c>
       <c r="B89" t="s">
@@ -5577,7 +5603,7 @@
       </c>
     </row>
     <row r="90" spans="1:14">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>45296</v>
       </c>
       <c r="B90" t="s">
@@ -5621,7 +5647,7 @@
       </c>
     </row>
     <row r="91" spans="1:14">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>45296</v>
       </c>
       <c r="B91" t="s">
@@ -5665,7 +5691,7 @@
       </c>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>45296</v>
       </c>
       <c r="B92" t="s">
@@ -5709,7 +5735,7 @@
       </c>
     </row>
     <row r="93" spans="1:14">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>45303</v>
       </c>
       <c r="B93" t="s">
@@ -5747,7 +5773,7 @@
       </c>
     </row>
     <row r="94" spans="1:14">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>45303</v>
       </c>
       <c r="B94" t="s">
@@ -5791,7 +5817,7 @@
       </c>
     </row>
     <row r="95" spans="1:14">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>45303</v>
       </c>
       <c r="B95" t="s">
@@ -5835,7 +5861,7 @@
       </c>
     </row>
     <row r="96" spans="1:14">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>45303</v>
       </c>
       <c r="B96" t="s">
@@ -5879,7 +5905,7 @@
       </c>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>45303</v>
       </c>
       <c r="B97" t="s">
@@ -5923,7 +5949,7 @@
       </c>
     </row>
     <row r="98" spans="1:14">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>45303</v>
       </c>
       <c r="B98" t="s">
@@ -5967,7 +5993,7 @@
       </c>
     </row>
     <row r="99" spans="1:14">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>45303</v>
       </c>
       <c r="B99" t="s">
@@ -6011,7 +6037,7 @@
       </c>
     </row>
     <row r="100" spans="1:14">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>45310</v>
       </c>
       <c r="B100" t="s">
@@ -6049,7 +6075,7 @@
       </c>
     </row>
     <row r="101" spans="1:14">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>45310</v>
       </c>
       <c r="B101" t="s">
@@ -6093,7 +6119,7 @@
       </c>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>45310</v>
       </c>
       <c r="B102" t="s">
@@ -6137,7 +6163,7 @@
       </c>
     </row>
     <row r="103" spans="1:14">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>45310</v>
       </c>
       <c r="B103" t="s">
@@ -6181,7 +6207,7 @@
       </c>
     </row>
     <row r="104" spans="1:14">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>45310</v>
       </c>
       <c r="B104" t="s">
@@ -6225,7 +6251,7 @@
       </c>
     </row>
     <row r="105" spans="1:14">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>45310</v>
       </c>
       <c r="B105" t="s">
@@ -6269,7 +6295,7 @@
       </c>
     </row>
     <row r="106" spans="1:14">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>45310</v>
       </c>
       <c r="B106" t="s">
@@ -6313,7 +6339,7 @@
       </c>
     </row>
     <row r="107" spans="1:14">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>45317</v>
       </c>
       <c r="B107" t="s">
@@ -6351,7 +6377,7 @@
       </c>
     </row>
     <row r="108" spans="1:14">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>45317</v>
       </c>
       <c r="B108" t="s">
@@ -6395,7 +6421,7 @@
       </c>
     </row>
     <row r="109" spans="1:14">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>45317</v>
       </c>
       <c r="B109" t="s">
@@ -6439,7 +6465,7 @@
       </c>
     </row>
     <row r="110" spans="1:14">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>45317</v>
       </c>
       <c r="B110" t="s">
@@ -6483,7 +6509,7 @@
       </c>
     </row>
     <row r="111" spans="1:14">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>45317</v>
       </c>
       <c r="B111" t="s">
@@ -6527,7 +6553,7 @@
       </c>
     </row>
     <row r="112" spans="1:14">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>45317</v>
       </c>
       <c r="B112" t="s">
@@ -6571,7 +6597,7 @@
       </c>
     </row>
     <row r="113" spans="1:14">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>45317</v>
       </c>
       <c r="B113" t="s">
@@ -6615,7 +6641,7 @@
       </c>
     </row>
     <row r="114" spans="1:14">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>45324</v>
       </c>
       <c r="B114" t="s">
@@ -6653,7 +6679,7 @@
       </c>
     </row>
     <row r="115" spans="1:14">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>45324</v>
       </c>
       <c r="B115" t="s">
@@ -6697,7 +6723,7 @@
       </c>
     </row>
     <row r="116" spans="1:14">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>45324</v>
       </c>
       <c r="B116" t="s">
@@ -6741,7 +6767,7 @@
       </c>
     </row>
     <row r="117" spans="1:14">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>45324</v>
       </c>
       <c r="B117" t="s">
@@ -6785,7 +6811,7 @@
       </c>
     </row>
     <row r="118" spans="1:14">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>45324</v>
       </c>
       <c r="B118" t="s">
@@ -6829,7 +6855,7 @@
       </c>
     </row>
     <row r="119" spans="1:14">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>45324</v>
       </c>
       <c r="B119" t="s">
@@ -6873,7 +6899,7 @@
       </c>
     </row>
     <row r="120" spans="1:14">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>45324</v>
       </c>
       <c r="B120" t="s">
@@ -6917,7 +6943,7 @@
       </c>
     </row>
     <row r="121" spans="1:14">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>45331</v>
       </c>
       <c r="B121" t="s">
@@ -6955,7 +6981,7 @@
       </c>
     </row>
     <row r="122" spans="1:14">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>45331</v>
       </c>
       <c r="B122" t="s">
@@ -6999,7 +7025,7 @@
       </c>
     </row>
     <row r="123" spans="1:14">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>45331</v>
       </c>
       <c r="B123" t="s">
@@ -7043,7 +7069,7 @@
       </c>
     </row>
     <row r="124" spans="1:14">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>45331</v>
       </c>
       <c r="B124" t="s">
@@ -7087,7 +7113,7 @@
       </c>
     </row>
     <row r="125" spans="1:14">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>45331</v>
       </c>
       <c r="B125" t="s">
@@ -7131,7 +7157,7 @@
       </c>
     </row>
     <row r="126" spans="1:14">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>45331</v>
       </c>
       <c r="B126" t="s">
@@ -7175,7 +7201,7 @@
       </c>
     </row>
     <row r="127" spans="1:14">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>45331</v>
       </c>
       <c r="B127" t="s">
@@ -7219,7 +7245,7 @@
       </c>
     </row>
     <row r="128" spans="1:14">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
@@ -7257,7 +7283,7 @@
       </c>
     </row>
     <row r="129" spans="1:14">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>45338</v>
       </c>
       <c r="B129" t="s">
@@ -7301,7 +7327,7 @@
       </c>
     </row>
     <row r="130" spans="1:14">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>45338</v>
       </c>
       <c r="B130" t="s">
@@ -7345,7 +7371,7 @@
       </c>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>45338</v>
       </c>
       <c r="B131" t="s">
@@ -7389,7 +7415,7 @@
       </c>
     </row>
     <row r="132" spans="1:14">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>45338</v>
       </c>
       <c r="B132" t="s">
@@ -7433,7 +7459,7 @@
       </c>
     </row>
     <row r="133" spans="1:14">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>45338</v>
       </c>
       <c r="B133" t="s">
@@ -7477,7 +7503,7 @@
       </c>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>45338</v>
       </c>
       <c r="B134" t="s">
@@ -7521,7 +7547,7 @@
       </c>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>45345</v>
       </c>
       <c r="B135" t="s">
@@ -7559,7 +7585,7 @@
       </c>
     </row>
     <row r="136" spans="1:14">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>45345</v>
       </c>
       <c r="B136" t="s">
@@ -7603,7 +7629,7 @@
       </c>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>45345</v>
       </c>
       <c r="B137" t="s">
@@ -7647,7 +7673,7 @@
       </c>
     </row>
     <row r="138" spans="1:14">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>45345</v>
       </c>
       <c r="B138" t="s">
@@ -7691,7 +7717,7 @@
       </c>
     </row>
     <row r="139" spans="1:14">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>45345</v>
       </c>
       <c r="B139" t="s">
@@ -7735,7 +7761,7 @@
       </c>
     </row>
     <row r="140" spans="1:14">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>45345</v>
       </c>
       <c r="B140" t="s">
@@ -7779,7 +7805,7 @@
       </c>
     </row>
     <row r="141" spans="1:14">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>45345</v>
       </c>
       <c r="B141" t="s">
@@ -7823,7 +7849,7 @@
       </c>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>45639</v>
       </c>
       <c r="B142" t="s">
@@ -7861,7 +7887,7 @@
       </c>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>45639</v>
       </c>
       <c r="B143" t="s">
@@ -7905,7 +7931,7 @@
       </c>
     </row>
     <row r="144" spans="1:14">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>45646</v>
       </c>
       <c r="B144" t="s">
@@ -7943,7 +7969,7 @@
       </c>
     </row>
     <row r="145" spans="1:14">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>45646</v>
       </c>
       <c r="B145" t="s">
@@ -7987,7 +8013,7 @@
       </c>
     </row>
     <row r="146" spans="1:14">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>45646</v>
       </c>
       <c r="B146" t="s">
@@ -8031,7 +8057,7 @@
       </c>
     </row>
     <row r="147" spans="1:14">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>45646</v>
       </c>
       <c r="B147" t="s">
@@ -8075,7 +8101,7 @@
       </c>
     </row>
     <row r="148" spans="1:14">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>45646</v>
       </c>
       <c r="B148" t="s">
@@ -8119,7 +8145,7 @@
       </c>
     </row>
     <row r="149" spans="1:14">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>45646</v>
       </c>
       <c r="B149" t="s">
@@ -8163,7 +8189,7 @@
       </c>
     </row>
     <row r="150" spans="1:14">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>45646</v>
       </c>
       <c r="B150" t="s">
@@ -8207,7 +8233,7 @@
       </c>
     </row>
     <row r="151" spans="1:14">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>45653</v>
       </c>
       <c r="B151" t="s">
@@ -8245,7 +8271,7 @@
       </c>
     </row>
     <row r="152" spans="1:14">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>45653</v>
       </c>
       <c r="B152" t="s">
@@ -8289,7 +8315,7 @@
       </c>
     </row>
     <row r="153" spans="1:14">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>45653</v>
       </c>
       <c r="B153" t="s">
@@ -8333,7 +8359,7 @@
       </c>
     </row>
     <row r="154" spans="1:14">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>45653</v>
       </c>
       <c r="B154" t="s">
@@ -8377,7 +8403,7 @@
       </c>
     </row>
     <row r="155" spans="1:14">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>45653</v>
       </c>
       <c r="B155" t="s">
@@ -8421,7 +8447,7 @@
       </c>
     </row>
     <row r="156" spans="1:14">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>45653</v>
       </c>
       <c r="B156" t="s">
@@ -8465,7 +8491,7 @@
       </c>
     </row>
     <row r="157" spans="1:14">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>45653</v>
       </c>
       <c r="B157" t="s">
@@ -8509,7 +8535,7 @@
       </c>
     </row>
     <row r="158" spans="1:14">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>45660</v>
       </c>
       <c r="B158" t="s">
@@ -8547,7 +8573,7 @@
       </c>
     </row>
     <row r="159" spans="1:14">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>45660</v>
       </c>
       <c r="B159" t="s">
@@ -8591,7 +8617,7 @@
       </c>
     </row>
     <row r="160" spans="1:14">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>45660</v>
       </c>
       <c r="B160" t="s">
@@ -8635,7 +8661,7 @@
       </c>
     </row>
     <row r="161" spans="1:14">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45660</v>
       </c>
       <c r="B161" t="s">
@@ -8679,7 +8705,7 @@
       </c>
     </row>
     <row r="162" spans="1:14">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45660</v>
       </c>
       <c r="B162" t="s">
@@ -8723,7 +8749,7 @@
       </c>
     </row>
     <row r="163" spans="1:14">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45660</v>
       </c>
       <c r="B163" t="s">
@@ -8767,7 +8793,7 @@
       </c>
     </row>
     <row r="164" spans="1:14">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45660</v>
       </c>
       <c r="B164" t="s">
@@ -8811,7 +8837,7 @@
       </c>
     </row>
     <row r="165" spans="1:14">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45667</v>
       </c>
       <c r="B165" t="s">
@@ -8849,7 +8875,7 @@
       </c>
     </row>
     <row r="166" spans="1:14">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45667</v>
       </c>
       <c r="B166" t="s">
@@ -8893,7 +8919,7 @@
       </c>
     </row>
     <row r="167" spans="1:14">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45667</v>
       </c>
       <c r="B167" t="s">
@@ -8937,7 +8963,7 @@
       </c>
     </row>
     <row r="168" spans="1:14">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45667</v>
       </c>
       <c r="B168" t="s">
@@ -8981,7 +9007,7 @@
       </c>
     </row>
     <row r="169" spans="1:14">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45667</v>
       </c>
       <c r="B169" t="s">
@@ -9025,7 +9051,7 @@
       </c>
     </row>
     <row r="170" spans="1:14">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45667</v>
       </c>
       <c r="B170" t="s">
@@ -9069,7 +9095,7 @@
       </c>
     </row>
     <row r="171" spans="1:14">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45667</v>
       </c>
       <c r="B171" t="s">
@@ -9113,7 +9139,7 @@
       </c>
     </row>
     <row r="172" spans="1:14">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45674</v>
       </c>
       <c r="B172" t="s">
@@ -9151,7 +9177,7 @@
       </c>
     </row>
     <row r="173" spans="1:14">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>45674</v>
       </c>
       <c r="B173" t="s">
@@ -9195,7 +9221,7 @@
       </c>
     </row>
     <row r="174" spans="1:14">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>45674</v>
       </c>
       <c r="B174" t="s">
@@ -9239,7 +9265,7 @@
       </c>
     </row>
     <row r="175" spans="1:14">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>45674</v>
       </c>
       <c r="B175" t="s">
@@ -9283,7 +9309,7 @@
       </c>
     </row>
     <row r="176" spans="1:14">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>45674</v>
       </c>
       <c r="B176" t="s">
@@ -9327,7 +9353,7 @@
       </c>
     </row>
     <row r="177" spans="1:14">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>45674</v>
       </c>
       <c r="B177" t="s">
@@ -9371,7 +9397,7 @@
       </c>
     </row>
     <row r="178" spans="1:14">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>45674</v>
       </c>
       <c r="B178" t="s">
@@ -9415,7 +9441,7 @@
       </c>
     </row>
     <row r="179" spans="1:14">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>45681</v>
       </c>
       <c r="B179" t="s">
@@ -9453,7 +9479,7 @@
       </c>
     </row>
     <row r="180" spans="1:14">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>45681</v>
       </c>
       <c r="B180" t="s">
@@ -9497,7 +9523,7 @@
       </c>
     </row>
     <row r="181" spans="1:14">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>45681</v>
       </c>
       <c r="B181" t="s">
@@ -9541,7 +9567,7 @@
       </c>
     </row>
     <row r="182" spans="1:14">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>45681</v>
       </c>
       <c r="B182" t="s">
@@ -9585,7 +9611,7 @@
       </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>45681</v>
       </c>
       <c r="B183" t="s">
@@ -9629,7 +9655,7 @@
       </c>
     </row>
     <row r="184" spans="1:14">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>45681</v>
       </c>
       <c r="B184" t="s">
@@ -9673,7 +9699,7 @@
       </c>
     </row>
     <row r="185" spans="1:14">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45681</v>
       </c>
       <c r="B185" t="s">
@@ -9717,7 +9743,7 @@
       </c>
     </row>
     <row r="186" spans="1:14">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45688</v>
       </c>
       <c r="B186" t="s">
@@ -9755,7 +9781,7 @@
       </c>
     </row>
     <row r="187" spans="1:14">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45688</v>
       </c>
       <c r="B187" t="s">
@@ -9799,7 +9825,7 @@
       </c>
     </row>
     <row r="188" spans="1:14">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45688</v>
       </c>
       <c r="B188" t="s">
@@ -9843,7 +9869,7 @@
       </c>
     </row>
     <row r="189" spans="1:14">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45688</v>
       </c>
       <c r="B189" t="s">
@@ -9887,7 +9913,7 @@
       </c>
     </row>
     <row r="190" spans="1:14">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45688</v>
       </c>
       <c r="B190" t="s">
@@ -9931,7 +9957,7 @@
       </c>
     </row>
     <row r="191" spans="1:14">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45688</v>
       </c>
       <c r="B191" t="s">
@@ -9975,7 +10001,7 @@
       </c>
     </row>
     <row r="192" spans="1:14">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45688</v>
       </c>
       <c r="B192" t="s">
@@ -10019,7 +10045,7 @@
       </c>
     </row>
     <row r="193" spans="1:14">
-      <c r="A193" s="1">
+      <c r="A193" s="2">
         <v>45695</v>
       </c>
       <c r="B193" t="s">
@@ -10057,7 +10083,7 @@
       </c>
     </row>
     <row r="194" spans="1:14">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>45695</v>
       </c>
       <c r="B194" t="s">
@@ -10101,7 +10127,7 @@
       </c>
     </row>
     <row r="195" spans="1:14">
-      <c r="A195" s="1">
+      <c r="A195" s="2">
         <v>45695</v>
       </c>
       <c r="B195" t="s">
@@ -10145,7 +10171,7 @@
       </c>
     </row>
     <row r="196" spans="1:14">
-      <c r="A196" s="1">
+      <c r="A196" s="2">
         <v>45695</v>
       </c>
       <c r="B196" t="s">
@@ -10189,7 +10215,7 @@
       </c>
     </row>
     <row r="197" spans="1:14">
-      <c r="A197" s="1">
+      <c r="A197" s="2">
         <v>45695</v>
       </c>
       <c r="B197" t="s">
@@ -10233,7 +10259,7 @@
       </c>
     </row>
     <row r="198" spans="1:14">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>45695</v>
       </c>
       <c r="B198" t="s">
@@ -10277,7 +10303,7 @@
       </c>
     </row>
     <row r="199" spans="1:14">
-      <c r="A199" s="1">
+      <c r="A199" s="2">
         <v>45695</v>
       </c>
       <c r="B199" t="s">
@@ -10321,7 +10347,7 @@
       </c>
     </row>
     <row r="200" spans="1:14">
-      <c r="A200" s="1">
+      <c r="A200" s="2">
         <v>45702</v>
       </c>
       <c r="B200" t="s">
@@ -10359,7 +10385,7 @@
       </c>
     </row>
     <row r="201" spans="1:14">
-      <c r="A201" s="1">
+      <c r="A201" s="2">
         <v>45702</v>
       </c>
       <c r="B201" t="s">
@@ -10403,7 +10429,7 @@
       </c>
     </row>
     <row r="202" spans="1:14">
-      <c r="A202" s="1">
+      <c r="A202" s="2">
         <v>45702</v>
       </c>
       <c r="B202" t="s">
@@ -10447,7 +10473,7 @@
       </c>
     </row>
     <row r="203" spans="1:14">
-      <c r="A203" s="1">
+      <c r="A203" s="2">
         <v>45702</v>
       </c>
       <c r="B203" t="s">
@@ -10491,7 +10517,7 @@
       </c>
     </row>
     <row r="204" spans="1:14">
-      <c r="A204" s="1">
+      <c r="A204" s="2">
         <v>45702</v>
       </c>
       <c r="B204" t="s">
@@ -10535,7 +10561,7 @@
       </c>
     </row>
     <row r="205" spans="1:14">
-      <c r="A205" s="1">
+      <c r="A205" s="2">
         <v>45702</v>
       </c>
       <c r="B205" t="s">
@@ -10579,7 +10605,7 @@
       </c>
     </row>
     <row r="206" spans="1:14">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>45702</v>
       </c>
       <c r="B206" t="s">
@@ -10623,7 +10649,7 @@
       </c>
     </row>
     <row r="207" spans="1:14">
-      <c r="A207" s="1">
+      <c r="A207" s="2">
         <v>45709</v>
       </c>
       <c r="B207" t="s">
@@ -10661,7 +10687,7 @@
       </c>
     </row>
     <row r="208" spans="1:14">
-      <c r="A208" s="1">
+      <c r="A208" s="2">
         <v>45709</v>
       </c>
       <c r="B208" t="s">
@@ -10705,7 +10731,7 @@
       </c>
     </row>
     <row r="209" spans="1:14">
-      <c r="A209" s="1">
+      <c r="A209" s="2">
         <v>45709</v>
       </c>
       <c r="B209" t="s">
@@ -10749,7 +10775,7 @@
       </c>
     </row>
     <row r="210" spans="1:14">
-      <c r="A210" s="1">
+      <c r="A210" s="2">
         <v>45709</v>
       </c>
       <c r="B210" t="s">
@@ -10793,7 +10819,7 @@
       </c>
     </row>
     <row r="211" spans="1:14">
-      <c r="A211" s="1">
+      <c r="A211" s="2">
         <v>45709</v>
       </c>
       <c r="B211" t="s">
@@ -10837,7 +10863,7 @@
       </c>
     </row>
     <row r="212" spans="1:14">
-      <c r="A212" s="1">
+      <c r="A212" s="2">
         <v>45709</v>
       </c>
       <c r="B212" t="s">
@@ -10881,7 +10907,7 @@
       </c>
     </row>
     <row r="213" spans="1:14">
-      <c r="A213" s="1">
+      <c r="A213" s="2">
         <v>45709</v>
       </c>
       <c r="B213" t="s">
@@ -10925,7 +10951,7 @@
       </c>
     </row>
     <row r="214" spans="1:14">
-      <c r="A214" s="1">
+      <c r="A214" s="2">
         <v>45716</v>
       </c>
       <c r="B214" t="s">
@@ -10963,7 +10989,7 @@
       </c>
     </row>
     <row r="215" spans="1:14">
-      <c r="A215" s="1">
+      <c r="A215" s="2">
         <v>45716</v>
       </c>
       <c r="B215" t="s">
@@ -11007,7 +11033,7 @@
       </c>
     </row>
     <row r="216" spans="1:14">
-      <c r="A216" s="1">
+      <c r="A216" s="2">
         <v>45716</v>
       </c>
       <c r="B216" t="s">
@@ -11051,7 +11077,7 @@
       </c>
     </row>
     <row r="217" spans="1:14">
-      <c r="A217" s="1">
+      <c r="A217" s="2">
         <v>45716</v>
       </c>
       <c r="B217" t="s">
@@ -11095,7 +11121,7 @@
       </c>
     </row>
     <row r="218" spans="1:14">
-      <c r="A218" s="1">
+      <c r="A218" s="2">
         <v>45716</v>
       </c>
       <c r="B218" t="s">
@@ -11139,7 +11165,7 @@
       </c>
     </row>
     <row r="219" spans="1:14">
-      <c r="A219" s="1">
+      <c r="A219" s="2">
         <v>45716</v>
       </c>
       <c r="B219" t="s">
@@ -11183,7 +11209,7 @@
       </c>
     </row>
     <row r="220" spans="1:14">
-      <c r="A220" s="1">
+      <c r="A220" s="2">
         <v>45716</v>
       </c>
       <c r="B220" t="s">
@@ -11227,7 +11253,7 @@
       </c>
     </row>
     <row r="221" spans="1:14">
-      <c r="A221" s="1">
+      <c r="A221" s="2">
         <v>46003</v>
       </c>
       <c r="B221" t="s">
@@ -11265,7 +11291,7 @@
       </c>
     </row>
     <row r="222" spans="1:14">
-      <c r="A222" s="1">
+      <c r="A222" s="2">
         <v>46003</v>
       </c>
       <c r="B222" t="s">
@@ -11309,7 +11335,7 @@
       </c>
     </row>
     <row r="223" spans="1:14">
-      <c r="A223" s="1">
+      <c r="A223" s="2">
         <v>46003</v>
       </c>
       <c r="B223" t="s">
@@ -11353,7 +11379,7 @@
       </c>
     </row>
     <row r="224" spans="1:14">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>46003</v>
       </c>
       <c r="B224" t="s">
@@ -11397,7 +11423,7 @@
       </c>
     </row>
     <row r="225" spans="1:14">
-      <c r="A225" s="1">
+      <c r="A225" s="2">
         <v>46003</v>
       </c>
       <c r="B225" t="s">
@@ -11441,7 +11467,7 @@
       </c>
     </row>
     <row r="226" spans="1:14">
-      <c r="A226" s="1">
+      <c r="A226" s="2">
         <v>46003</v>
       </c>
       <c r="B226" t="s">
@@ -11485,7 +11511,7 @@
       </c>
     </row>
     <row r="227" spans="1:14">
-      <c r="A227" s="1">
+      <c r="A227" s="2">
         <v>46003</v>
       </c>
       <c r="B227" t="s">
@@ -11529,7 +11555,7 @@
       </c>
     </row>
     <row r="228" spans="1:14">
-      <c r="A228" s="1">
+      <c r="A228" s="2">
         <v>46010</v>
       </c>
       <c r="B228" t="s">
@@ -11567,7 +11593,7 @@
       </c>
     </row>
     <row r="229" spans="1:14">
-      <c r="A229" s="1">
+      <c r="A229" s="2">
         <v>46010</v>
       </c>
       <c r="B229" t="s">
@@ -11608,7 +11634,7 @@
       </c>
     </row>
     <row r="230" spans="1:14">
-      <c r="A230" s="1">
+      <c r="A230" s="2">
         <v>46010</v>
       </c>
       <c r="B230" t="s">
@@ -11649,7 +11675,7 @@
       </c>
     </row>
     <row r="231" spans="1:14">
-      <c r="A231" s="1">
+      <c r="A231" s="2">
         <v>46010</v>
       </c>
       <c r="B231" t="s">
@@ -11690,7 +11716,7 @@
       </c>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="1">
+      <c r="A232" s="2">
         <v>46010</v>
       </c>
       <c r="B232" t="s">
@@ -11731,7 +11757,7 @@
       </c>
     </row>
     <row r="233" spans="1:14">
-      <c r="A233" s="1">
+      <c r="A233" s="2">
         <v>46010</v>
       </c>
       <c r="B233" t="s">
@@ -11772,7 +11798,7 @@
       </c>
     </row>
     <row r="234" spans="1:14">
-      <c r="A234" s="1">
+      <c r="A234" s="2">
         <v>46010</v>
       </c>
       <c r="B234" t="s">
@@ -11816,7 +11842,7 @@
       </c>
     </row>
     <row r="235" spans="1:14">
-      <c r="A235" s="1">
+      <c r="A235" s="2">
         <v>46017</v>
       </c>
       <c r="B235" t="s">
@@ -11854,7 +11880,7 @@
       </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="1">
+      <c r="A236" s="2">
         <v>46017</v>
       </c>
       <c r="B236" t="s">
@@ -11898,7 +11924,7 @@
       </c>
     </row>
     <row r="237" spans="1:14">
-      <c r="A237" s="1">
+      <c r="A237" s="2">
         <v>46017</v>
       </c>
       <c r="B237" t="s">
@@ -11942,7 +11968,7 @@
       </c>
     </row>
     <row r="238" spans="1:14">
-      <c r="A238" s="1">
+      <c r="A238" s="2">
         <v>46017</v>
       </c>
       <c r="B238" t="s">
@@ -11986,7 +12012,7 @@
       </c>
     </row>
     <row r="239" spans="1:14">
-      <c r="A239" s="1">
+      <c r="A239" s="2">
         <v>46017</v>
       </c>
       <c r="B239" t="s">
@@ -12030,7 +12056,7 @@
       </c>
     </row>
     <row r="240" spans="1:14">
-      <c r="A240" s="1">
+      <c r="A240" s="2">
         <v>46017</v>
       </c>
       <c r="B240" t="s">
@@ -12074,7 +12100,7 @@
       </c>
     </row>
     <row r="241" spans="1:14">
-      <c r="A241" s="1">
+      <c r="A241" s="2">
         <v>46017</v>
       </c>
       <c r="B241" t="s">
@@ -12118,7 +12144,7 @@
       </c>
     </row>
     <row r="242" spans="1:14">
-      <c r="A242" s="1">
+      <c r="A242" s="2">
         <v>46024</v>
       </c>
       <c r="B242" t="s">
@@ -12156,7 +12182,7 @@
       </c>
     </row>
     <row r="243" spans="1:14">
-      <c r="A243" s="1">
+      <c r="A243" s="2">
         <v>46024</v>
       </c>
       <c r="B243" t="s">
@@ -12200,7 +12226,7 @@
       </c>
     </row>
     <row r="244" spans="1:14">
-      <c r="A244" s="1">
+      <c r="A244" s="2">
         <v>46024</v>
       </c>
       <c r="B244" t="s">
@@ -12244,7 +12270,7 @@
       </c>
     </row>
     <row r="245" spans="1:14">
-      <c r="A245" s="1">
+      <c r="A245" s="2">
         <v>46024</v>
       </c>
       <c r="B245" t="s">
@@ -12288,7 +12314,7 @@
       </c>
     </row>
     <row r="246" spans="1:14">
-      <c r="A246" s="1">
+      <c r="A246" s="2">
         <v>46024</v>
       </c>
       <c r="B246" t="s">
@@ -12332,7 +12358,7 @@
       </c>
     </row>
     <row r="247" spans="1:14">
-      <c r="A247" s="1">
+      <c r="A247" s="2">
         <v>46024</v>
       </c>
       <c r="B247" t="s">
@@ -12376,7 +12402,7 @@
       </c>
     </row>
     <row r="248" spans="1:14">
-      <c r="A248" s="1">
+      <c r="A248" s="2">
         <v>46024</v>
       </c>
       <c r="B248" t="s">
@@ -12420,7 +12446,7 @@
       </c>
     </row>
     <row r="249" spans="1:14">
-      <c r="A249" s="1">
+      <c r="A249" s="2">
         <v>46031</v>
       </c>
       <c r="B249" t="s">
@@ -12458,7 +12484,7 @@
       </c>
     </row>
     <row r="250" spans="1:14">
-      <c r="A250" s="1">
+      <c r="A250" s="2">
         <v>46031</v>
       </c>
       <c r="B250" t="s">
@@ -12502,7 +12528,7 @@
       </c>
     </row>
     <row r="251" spans="1:14">
-      <c r="A251" s="1">
+      <c r="A251" s="2">
         <v>46031</v>
       </c>
       <c r="B251" t="s">
@@ -12546,7 +12572,7 @@
       </c>
     </row>
     <row r="252" spans="1:14">
-      <c r="A252" s="1">
+      <c r="A252" s="2">
         <v>46031</v>
       </c>
       <c r="B252" t="s">
@@ -12590,7 +12616,7 @@
       </c>
     </row>
     <row r="253" spans="1:14">
-      <c r="A253" s="1">
+      <c r="A253" s="2">
         <v>46031</v>
       </c>
       <c r="B253" t="s">
@@ -12634,7 +12660,7 @@
       </c>
     </row>
     <row r="254" spans="1:14">
-      <c r="A254" s="1">
+      <c r="A254" s="2">
         <v>46031</v>
       </c>
       <c r="B254" t="s">
@@ -12678,7 +12704,7 @@
       </c>
     </row>
     <row r="255" spans="1:14">
-      <c r="A255" s="1">
+      <c r="A255" s="2">
         <v>46031</v>
       </c>
       <c r="B255" t="s">
@@ -12722,7 +12748,7 @@
       </c>
     </row>
     <row r="256" spans="1:14">
-      <c r="A256" s="1">
+      <c r="A256" s="2">
         <v>46038</v>
       </c>
       <c r="B256" t="s">
@@ -12760,7 +12786,7 @@
       </c>
     </row>
     <row r="257" spans="1:14">
-      <c r="A257" s="1">
+      <c r="A257" s="2">
         <v>46038</v>
       </c>
       <c r="B257" t="s">
@@ -12804,7 +12830,7 @@
       </c>
     </row>
     <row r="258" spans="1:14">
-      <c r="A258" s="1">
+      <c r="A258" s="2">
         <v>46038</v>
       </c>
       <c r="B258" t="s">
@@ -12848,7 +12874,7 @@
       </c>
     </row>
     <row r="259" spans="1:14">
-      <c r="A259" s="1">
+      <c r="A259" s="2">
         <v>46038</v>
       </c>
       <c r="B259" t="s">
@@ -12892,7 +12918,7 @@
       </c>
     </row>
     <row r="260" spans="1:14">
-      <c r="A260" s="1">
+      <c r="A260" s="2">
         <v>46038</v>
       </c>
       <c r="B260" t="s">
@@ -12936,7 +12962,7 @@
       </c>
     </row>
     <row r="261" spans="1:14">
-      <c r="A261" s="1">
+      <c r="A261" s="2">
         <v>46038</v>
       </c>
       <c r="B261" t="s">
@@ -12980,7 +13006,7 @@
       </c>
     </row>
     <row r="262" spans="1:14">
-      <c r="A262" s="1">
+      <c r="A262" s="2">
         <v>46038</v>
       </c>
       <c r="B262" t="s">
@@ -13024,7 +13050,7 @@
       </c>
     </row>
     <row r="263" spans="1:14">
-      <c r="A263" s="1">
+      <c r="A263" s="2">
         <v>46045</v>
       </c>
       <c r="B263" t="s">
@@ -13062,7 +13088,7 @@
       </c>
     </row>
     <row r="264" spans="1:14">
-      <c r="A264" s="1">
+      <c r="A264" s="2">
         <v>46045</v>
       </c>
       <c r="B264" t="s">
@@ -13106,7 +13132,7 @@
       </c>
     </row>
     <row r="265" spans="1:14">
-      <c r="A265" s="1">
+      <c r="A265" s="2">
         <v>46045</v>
       </c>
       <c r="B265" t="s">
@@ -13150,7 +13176,7 @@
       </c>
     </row>
     <row r="266" spans="1:14">
-      <c r="A266" s="1">
+      <c r="A266" s="2">
         <v>46045</v>
       </c>
       <c r="B266" t="s">
@@ -13194,7 +13220,7 @@
       </c>
     </row>
     <row r="267" spans="1:14">
-      <c r="A267" s="1">
+      <c r="A267" s="2">
         <v>46045</v>
       </c>
       <c r="B267" t="s">
@@ -13238,7 +13264,7 @@
       </c>
     </row>
     <row r="268" spans="1:14">
-      <c r="A268" s="1">
+      <c r="A268" s="2">
         <v>46045</v>
       </c>
       <c r="B268" t="s">
@@ -13282,7 +13308,7 @@
       </c>
     </row>
     <row r="269" spans="1:14">
-      <c r="A269" s="1">
+      <c r="A269" s="2">
         <v>46045</v>
       </c>
       <c r="B269" t="s">
@@ -13326,7 +13352,7 @@
       </c>
     </row>
     <row r="270" spans="1:14">
-      <c r="A270" s="1">
+      <c r="A270" s="2">
         <v>46052</v>
       </c>
       <c r="B270" t="s">
@@ -13364,7 +13390,7 @@
       </c>
     </row>
     <row r="271" spans="1:14">
-      <c r="A271" s="1">
+      <c r="A271" s="2">
         <v>46052</v>
       </c>
       <c r="B271" t="s">
@@ -13408,7 +13434,7 @@
       </c>
     </row>
     <row r="272" spans="1:14">
-      <c r="A272" s="1">
+      <c r="A272" s="2">
         <v>46052</v>
       </c>
       <c r="B272" t="s">
@@ -13452,7 +13478,7 @@
       </c>
     </row>
     <row r="273" spans="1:14">
-      <c r="A273" s="1">
+      <c r="A273" s="2">
         <v>46052</v>
       </c>
       <c r="B273" t="s">
@@ -13496,7 +13522,7 @@
       </c>
     </row>
     <row r="274" spans="1:14">
-      <c r="A274" s="1">
+      <c r="A274" s="2">
         <v>46052</v>
       </c>
       <c r="B274" t="s">
@@ -13540,7 +13566,7 @@
       </c>
     </row>
     <row r="275" spans="1:14">
-      <c r="A275" s="1">
+      <c r="A275" s="2">
         <v>46052</v>
       </c>
       <c r="B275" t="s">
@@ -13584,7 +13610,7 @@
       </c>
     </row>
     <row r="276" spans="1:14">
-      <c r="A276" s="1">
+      <c r="A276" s="2">
         <v>46052</v>
       </c>
       <c r="B276" t="s">
@@ -13628,7 +13654,7 @@
       </c>
     </row>
     <row r="277" spans="1:14">
-      <c r="A277" s="1">
+      <c r="A277" s="2">
         <v>46059</v>
       </c>
       <c r="B277" t="s">
@@ -13666,7 +13692,7 @@
       </c>
     </row>
     <row r="278" spans="1:14">
-      <c r="A278" s="1">
+      <c r="A278" s="2">
         <v>46059</v>
       </c>
       <c r="B278" t="s">
@@ -13710,7 +13736,7 @@
       </c>
     </row>
     <row r="279" spans="1:14">
-      <c r="A279" s="1">
+      <c r="A279" s="2">
         <v>46059</v>
       </c>
       <c r="B279" t="s">
@@ -13754,7 +13780,7 @@
       </c>
     </row>
     <row r="280" spans="1:14">
-      <c r="A280" s="1">
+      <c r="A280" s="2">
         <v>46059</v>
       </c>
       <c r="B280" t="s">
@@ -13798,7 +13824,7 @@
       </c>
     </row>
     <row r="281" spans="1:14">
-      <c r="A281" s="1">
+      <c r="A281" s="2">
         <v>46059</v>
       </c>
       <c r="B281" t="s">
@@ -13842,7 +13868,7 @@
       </c>
     </row>
     <row r="282" spans="1:14">
-      <c r="A282" s="1">
+      <c r="A282" s="2">
         <v>46059</v>
       </c>
       <c r="B282" t="s">
@@ -13886,7 +13912,7 @@
       </c>
     </row>
     <row r="283" spans="1:14">
-      <c r="A283" s="1">
+      <c r="A283" s="2">
         <v>46059</v>
       </c>
       <c r="B283" t="s">
@@ -13930,7 +13956,7 @@
       </c>
     </row>
     <row r="284" spans="1:14">
-      <c r="A284" s="1">
+      <c r="A284" s="2">
         <v>46066</v>
       </c>
       <c r="B284" t="s">
@@ -13968,7 +13994,7 @@
       </c>
     </row>
     <row r="285" spans="1:14">
-      <c r="A285" s="1">
+      <c r="A285" s="2">
         <v>46066</v>
       </c>
       <c r="B285" t="s">
@@ -14012,7 +14038,7 @@
       </c>
     </row>
     <row r="286" spans="1:14">
-      <c r="A286" s="1">
+      <c r="A286" s="2">
         <v>46066</v>
       </c>
       <c r="B286" t="s">
@@ -14056,7 +14082,7 @@
       </c>
     </row>
     <row r="287" spans="1:14">
-      <c r="A287" s="1">
+      <c r="A287" s="2">
         <v>46066</v>
       </c>
       <c r="B287" t="s">
@@ -14100,7 +14126,7 @@
       </c>
     </row>
     <row r="288" spans="1:14">
-      <c r="A288" s="1">
+      <c r="A288" s="2">
         <v>46066</v>
       </c>
       <c r="B288" t="s">
@@ -14144,7 +14170,7 @@
       </c>
     </row>
     <row r="289" spans="1:14">
-      <c r="A289" s="1">
+      <c r="A289" s="2">
         <v>46066</v>
       </c>
       <c r="B289" t="s">
@@ -14188,7 +14214,7 @@
       </c>
     </row>
     <row r="290" spans="1:14">
-      <c r="A290" s="1">
+      <c r="A290" s="2">
         <v>46066</v>
       </c>
       <c r="B290" t="s">
@@ -14232,7 +14258,7 @@
       </c>
     </row>
     <row r="291" spans="1:14">
-      <c r="A291" s="1">
+      <c r="A291" s="2">
         <v>46073</v>
       </c>
       <c r="B291" t="s">
@@ -14270,7 +14296,7 @@
       </c>
     </row>
     <row r="292" spans="1:14">
-      <c r="A292" s="1">
+      <c r="A292" s="2">
         <v>46073</v>
       </c>
       <c r="B292" t="s">
@@ -14314,7 +14340,7 @@
       </c>
     </row>
     <row r="293" spans="1:14">
-      <c r="A293" s="1">
+      <c r="A293" s="2">
         <v>46073</v>
       </c>
       <c r="B293" t="s">
@@ -14358,7 +14384,7 @@
       </c>
     </row>
     <row r="294" spans="1:14">
-      <c r="A294" s="1">
+      <c r="A294" s="2">
         <v>46073</v>
       </c>
       <c r="B294" t="s">
@@ -14402,7 +14428,7 @@
       </c>
     </row>
     <row r="295" spans="1:14">
-      <c r="A295" s="1">
+      <c r="A295" s="2">
         <v>46073</v>
       </c>
       <c r="B295" t="s">
@@ -14446,7 +14472,7 @@
       </c>
     </row>
     <row r="296" spans="1:14">
-      <c r="A296" s="1">
+      <c r="A296" s="2">
         <v>46073</v>
       </c>
       <c r="B296" t="s">
@@ -14490,7 +14516,7 @@
       </c>
     </row>
     <row r="297" spans="1:14">
-      <c r="A297" s="1">
+      <c r="A297" s="2">
         <v>46073</v>
       </c>
       <c r="B297" t="s">
@@ -14534,7 +14560,7 @@
       </c>
     </row>
     <row r="298" spans="1:14">
-      <c r="A298" s="1">
+      <c r="A298" s="2">
         <v>46080</v>
       </c>
       <c r="B298" t="s">
@@ -14572,7 +14598,7 @@
       </c>
     </row>
     <row r="299" spans="1:14">
-      <c r="A299" s="1">
+      <c r="A299" s="2">
         <v>46080</v>
       </c>
       <c r="B299" t="s">
@@ -14616,7 +14642,7 @@
       </c>
     </row>
     <row r="300" spans="1:14">
-      <c r="A300" s="1">
+      <c r="A300" s="2">
         <v>46080</v>
       </c>
       <c r="B300" t="s">
@@ -14660,7 +14686,7 @@
       </c>
     </row>
     <row r="301" spans="1:14">
-      <c r="A301" s="1">
+      <c r="A301" s="2">
         <v>46080</v>
       </c>
       <c r="B301" t="s">
@@ -14704,7 +14730,7 @@
       </c>
     </row>
     <row r="302" spans="1:14">
-      <c r="A302" s="1">
+      <c r="A302" s="2">
         <v>46080</v>
       </c>
       <c r="B302" t="s">
@@ -14748,7 +14774,7 @@
       </c>
     </row>
     <row r="303" spans="1:14">
-      <c r="A303" s="1">
+      <c r="A303" s="2">
         <v>46080</v>
       </c>
       <c r="B303" t="s">
@@ -14792,7 +14818,7 @@
       </c>
     </row>
     <row r="304" spans="1:14">
-      <c r="A304" s="1">
+      <c r="A304" s="2">
         <v>46080</v>
       </c>
       <c r="B304" t="s">
@@ -14846,36 +14872,36 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44932</v>
       </c>
       <c r="B2" t="s">
@@ -14904,7 +14930,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44939</v>
       </c>
       <c r="B3" t="s">
@@ -14933,7 +14959,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44946</v>
       </c>
       <c r="B4" t="s">
@@ -14962,7 +14988,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>44953</v>
       </c>
       <c r="B5" t="s">
@@ -14991,7 +15017,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>44960</v>
       </c>
       <c r="B6" t="s">
@@ -15020,7 +15046,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>44967</v>
       </c>
       <c r="B7" t="s">
@@ -15049,7 +15075,7 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>44974</v>
       </c>
       <c r="B8" t="s">
@@ -15078,7 +15104,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>44981</v>
       </c>
       <c r="B9" t="s">
@@ -15107,7 +15133,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>44988</v>
       </c>
       <c r="B10" t="s">
@@ -15136,7 +15162,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>45268</v>
       </c>
       <c r="B11" t="s">
@@ -15150,7 +15176,7 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>45275</v>
       </c>
       <c r="B12" t="s">
@@ -15173,7 +15199,7 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>45282</v>
       </c>
       <c r="B13" t="s">
@@ -15202,7 +15228,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>45289</v>
       </c>
       <c r="B14" t="s">
@@ -15231,7 +15257,7 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>45296</v>
       </c>
       <c r="B15" t="s">
@@ -15260,7 +15286,7 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>45303</v>
       </c>
       <c r="B16" t="s">
@@ -15289,7 +15315,7 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>45310</v>
       </c>
       <c r="B17" t="s">
@@ -15318,7 +15344,7 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>45317</v>
       </c>
       <c r="B18" t="s">
@@ -15347,7 +15373,7 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>45324</v>
       </c>
       <c r="B19" t="s">
@@ -15376,7 +15402,7 @@
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>45331</v>
       </c>
       <c r="B20" t="s">
@@ -15405,7 +15431,7 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>45338</v>
       </c>
       <c r="B21" t="s">
@@ -15434,7 +15460,7 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>45345</v>
       </c>
       <c r="B22" t="s">
@@ -15463,7 +15489,7 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>45639</v>
       </c>
       <c r="B23" t="s">
@@ -15477,7 +15503,7 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>45646</v>
       </c>
       <c r="B24" t="s">
@@ -15506,7 +15532,7 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>45653</v>
       </c>
       <c r="B25" t="s">
@@ -15535,7 +15561,7 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>45660</v>
       </c>
       <c r="B26" t="s">
@@ -15564,7 +15590,7 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>45667</v>
       </c>
       <c r="B27" t="s">
@@ -15593,7 +15619,7 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>45674</v>
       </c>
       <c r="B28" t="s">
@@ -15622,7 +15648,7 @@
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>45681</v>
       </c>
       <c r="B29" t="s">
@@ -15651,7 +15677,7 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>45688</v>
       </c>
       <c r="B30" t="s">
@@ -15680,7 +15706,7 @@
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>45695</v>
       </c>
       <c r="B31" t="s">
@@ -15709,7 +15735,7 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>45702</v>
       </c>
       <c r="B32" t="s">
@@ -15738,7 +15764,7 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>45709</v>
       </c>
       <c r="B33" t="s">
@@ -15767,7 +15793,7 @@
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>45716</v>
       </c>
       <c r="B34" t="s">
@@ -15796,7 +15822,7 @@
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>46003</v>
       </c>
       <c r="B35" t="s">
@@ -15825,7 +15851,7 @@
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>46010</v>
       </c>
       <c r="B36" t="s">
@@ -15854,7 +15880,7 @@
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>46017</v>
       </c>
       <c r="B37" t="s">
@@ -15883,7 +15909,7 @@
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>46024</v>
       </c>
       <c r="B38" t="s">
@@ -15912,7 +15938,7 @@
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>46031</v>
       </c>
       <c r="B39" t="s">
@@ -15941,7 +15967,7 @@
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>46038</v>
       </c>
       <c r="B40" t="s">
@@ -15970,7 +15996,7 @@
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>46045</v>
       </c>
       <c r="B41" t="s">
@@ -15999,7 +16025,7 @@
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>46052</v>
       </c>
       <c r="B42" t="s">
@@ -16028,7 +16054,7 @@
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>46059</v>
       </c>
       <c r="B43" t="s">
@@ -16057,7 +16083,7 @@
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>46066</v>
       </c>
       <c r="B44" t="s">
@@ -16086,7 +16112,7 @@
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>46073</v>
       </c>
       <c r="B45" t="s">
@@ -16115,7 +16141,7 @@
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>46080</v>
       </c>
       <c r="B46" t="s">
@@ -16154,31 +16180,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -16186,25 +16212,25 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>44932</v>
       </c>
       <c r="C2">
         <v>13.3349451044104</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>45268</v>
       </c>
       <c r="E2">
         <v>0.264958371381719</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>45639</v>
       </c>
       <c r="G2">
         <v>0.0979444014483086</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>46003</v>
       </c>
       <c r="I2">
@@ -16215,25 +16241,25 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>44939</v>
       </c>
       <c r="C3">
         <v>14.6310643820888</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>45275</v>
       </c>
       <c r="E3">
         <v>0.916702360323984</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>45646</v>
       </c>
       <c r="G3">
         <v>3.52641131291434</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>46010</v>
       </c>
       <c r="I3">
@@ -16244,25 +16270,25 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>44946</v>
       </c>
       <c r="C4">
         <v>25.470681466846</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>45282</v>
       </c>
       <c r="E4">
         <v>2.52675636188476</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45653</v>
       </c>
       <c r="G4">
         <v>6.85053439282485</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>46017</v>
       </c>
       <c r="I4">
@@ -16273,25 +16299,25 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>44953</v>
       </c>
       <c r="C5">
         <v>47.8078134776635</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>45289</v>
       </c>
       <c r="E5">
         <v>13.296123244575</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>45660</v>
       </c>
       <c r="G5">
         <v>10.2909375965284</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>46024</v>
       </c>
       <c r="I5">
@@ -16302,25 +16328,25 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>44960</v>
       </c>
       <c r="C6">
         <v>67.3723167138333</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>45296</v>
       </c>
       <c r="E6">
         <v>25.7190702289397</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45667</v>
       </c>
       <c r="G6">
         <v>14.1990297421458</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>46031</v>
       </c>
       <c r="I6">
@@ -16331,25 +16357,25 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>44967</v>
       </c>
       <c r="C7">
         <v>81.6287151148194</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>45303</v>
       </c>
       <c r="E7">
         <v>36.6579508054309</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45674</v>
       </c>
       <c r="G7">
         <v>19.34</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>46038</v>
       </c>
       <c r="I7">
@@ -16360,25 +16386,25 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>44974</v>
       </c>
       <c r="C8">
         <v>96.174071186535</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>45310</v>
       </c>
       <c r="E8">
         <v>56.4783427120612</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45681</v>
       </c>
       <c r="G8">
         <v>28.5674452200412</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>46045</v>
       </c>
       <c r="I8">
@@ -16389,25 +16415,25 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>44981</v>
       </c>
       <c r="C9">
         <v>99.9618132251632</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>45317</v>
       </c>
       <c r="E9">
         <v>77.0516355462711</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45688</v>
       </c>
       <c r="G9">
         <v>53.4778212935941</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>46052</v>
       </c>
       <c r="I9">
@@ -16418,25 +16444,25 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>44988</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>45324</v>
       </c>
       <c r="E10">
         <v>95.37381819513389</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>45695</v>
       </c>
       <c r="G10">
         <v>79.5566131134287</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>46059</v>
       </c>
       <c r="I10">
@@ -16447,19 +16473,19 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>45331</v>
       </c>
       <c r="E11">
         <v>98.8692321725709</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45702</v>
       </c>
       <c r="G11">
         <v>95.6802233981485</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>46066</v>
       </c>
       <c r="I11">
@@ -16470,19 +16496,19 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>45338</v>
       </c>
       <c r="E12">
         <v>99.9738010512051</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>45709</v>
       </c>
       <c r="G12">
         <v>99.92799255644471</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="2">
         <v>46073</v>
       </c>
       <c r="I12">
@@ -16493,19 +16519,19 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>45345</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>45716</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="2">
         <v>46080</v>
       </c>
       <c r="I13">
@@ -16523,196 +16549,196 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:64">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>117</v>
       </c>
     </row>
@@ -16813,7 +16839,7 @@
       <c r="AY2" t="s">
         <v>23</v>
       </c>
-      <c r="AZ2" s="1">
+      <c r="AZ2" s="2">
         <v>44932</v>
       </c>
       <c r="BA2" t="s">
@@ -16929,7 +16955,7 @@
       <c r="AY3" t="s">
         <v>24</v>
       </c>
-      <c r="AZ3" s="1">
+      <c r="AZ3" s="2">
         <v>44932</v>
       </c>
       <c r="BA3" t="s">
@@ -17045,7 +17071,7 @@
       <c r="AY4" t="s">
         <v>24</v>
       </c>
-      <c r="AZ4" s="1">
+      <c r="AZ4" s="2">
         <v>44932</v>
       </c>
       <c r="BA4" t="s">
@@ -17161,7 +17187,7 @@
       <c r="AY5" t="s">
         <v>24</v>
       </c>
-      <c r="AZ5" s="1">
+      <c r="AZ5" s="2">
         <v>44932</v>
       </c>
       <c r="BA5" t="s">
@@ -17277,7 +17303,7 @@
       <c r="AY6" t="s">
         <v>24</v>
       </c>
-      <c r="AZ6" s="1">
+      <c r="AZ6" s="2">
         <v>44932</v>
       </c>
       <c r="BA6" t="s">
@@ -17393,7 +17419,7 @@
       <c r="AY7" t="s">
         <v>24</v>
       </c>
-      <c r="AZ7" s="1">
+      <c r="AZ7" s="2">
         <v>44932</v>
       </c>
       <c r="BA7" t="s">
@@ -17509,7 +17535,7 @@
       <c r="AY8" t="s">
         <v>24</v>
       </c>
-      <c r="AZ8" s="1">
+      <c r="AZ8" s="2">
         <v>44932</v>
       </c>
       <c r="BA8" t="s">
@@ -17616,7 +17642,7 @@
       <c r="AY9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ9" s="1">
+      <c r="AZ9" s="2">
         <v>44939</v>
       </c>
       <c r="BA9" t="s">
@@ -17735,7 +17761,7 @@
       <c r="AY10" t="s">
         <v>24</v>
       </c>
-      <c r="AZ10" s="1">
+      <c r="AZ10" s="2">
         <v>44939</v>
       </c>
       <c r="BA10" t="s">
@@ -17854,7 +17880,7 @@
       <c r="AY11" t="s">
         <v>24</v>
       </c>
-      <c r="AZ11" s="1">
+      <c r="AZ11" s="2">
         <v>44939</v>
       </c>
       <c r="BA11" t="s">
@@ -17973,7 +17999,7 @@
       <c r="AY12" t="s">
         <v>24</v>
       </c>
-      <c r="AZ12" s="1">
+      <c r="AZ12" s="2">
         <v>44939</v>
       </c>
       <c r="BA12" t="s">
@@ -18092,7 +18118,7 @@
       <c r="AY13" t="s">
         <v>24</v>
       </c>
-      <c r="AZ13" s="1">
+      <c r="AZ13" s="2">
         <v>44939</v>
       </c>
       <c r="BA13" t="s">
@@ -18211,7 +18237,7 @@
       <c r="AY14" t="s">
         <v>24</v>
       </c>
-      <c r="AZ14" s="1">
+      <c r="AZ14" s="2">
         <v>44939</v>
       </c>
       <c r="BA14" t="s">
@@ -18330,7 +18356,7 @@
       <c r="AY15" t="s">
         <v>24</v>
       </c>
-      <c r="AZ15" s="1">
+      <c r="AZ15" s="2">
         <v>44939</v>
       </c>
       <c r="BA15" t="s">
@@ -18437,7 +18463,7 @@
       <c r="AY16" t="s">
         <v>23</v>
       </c>
-      <c r="AZ16" s="1">
+      <c r="AZ16" s="2">
         <v>44946</v>
       </c>
       <c r="BA16" t="s">
@@ -18556,7 +18582,7 @@
       <c r="AY17" t="s">
         <v>24</v>
       </c>
-      <c r="AZ17" s="1">
+      <c r="AZ17" s="2">
         <v>44946</v>
       </c>
       <c r="BA17" t="s">
@@ -18675,7 +18701,7 @@
       <c r="AY18" t="s">
         <v>24</v>
       </c>
-      <c r="AZ18" s="1">
+      <c r="AZ18" s="2">
         <v>44946</v>
       </c>
       <c r="BA18" t="s">
@@ -18794,7 +18820,7 @@
       <c r="AY19" t="s">
         <v>24</v>
       </c>
-      <c r="AZ19" s="1">
+      <c r="AZ19" s="2">
         <v>44946</v>
       </c>
       <c r="BA19" t="s">
@@ -18913,7 +18939,7 @@
       <c r="AY20" t="s">
         <v>24</v>
       </c>
-      <c r="AZ20" s="1">
+      <c r="AZ20" s="2">
         <v>44946</v>
       </c>
       <c r="BA20" t="s">
@@ -19032,7 +19058,7 @@
       <c r="AY21" t="s">
         <v>24</v>
       </c>
-      <c r="AZ21" s="1">
+      <c r="AZ21" s="2">
         <v>44946</v>
       </c>
       <c r="BA21" t="s">
@@ -19151,7 +19177,7 @@
       <c r="AY22" t="s">
         <v>24</v>
       </c>
-      <c r="AZ22" s="1">
+      <c r="AZ22" s="2">
         <v>44946</v>
       </c>
       <c r="BA22" t="s">
@@ -19261,7 +19287,7 @@
       <c r="AY23" t="s">
         <v>23</v>
       </c>
-      <c r="AZ23" s="1">
+      <c r="AZ23" s="2">
         <v>44953</v>
       </c>
       <c r="BA23" t="s">
@@ -19380,7 +19406,7 @@
       <c r="AY24" t="s">
         <v>24</v>
       </c>
-      <c r="AZ24" s="1">
+      <c r="AZ24" s="2">
         <v>44953</v>
       </c>
       <c r="BA24" t="s">
@@ -19499,7 +19525,7 @@
       <c r="AY25" t="s">
         <v>24</v>
       </c>
-      <c r="AZ25" s="1">
+      <c r="AZ25" s="2">
         <v>44953</v>
       </c>
       <c r="BA25" t="s">
@@ -19618,7 +19644,7 @@
       <c r="AY26" t="s">
         <v>24</v>
       </c>
-      <c r="AZ26" s="1">
+      <c r="AZ26" s="2">
         <v>44953</v>
       </c>
       <c r="BA26" t="s">
@@ -19737,7 +19763,7 @@
       <c r="AY27" t="s">
         <v>24</v>
       </c>
-      <c r="AZ27" s="1">
+      <c r="AZ27" s="2">
         <v>44953</v>
       </c>
       <c r="BA27" t="s">
@@ -19856,7 +19882,7 @@
       <c r="AY28" t="s">
         <v>24</v>
       </c>
-      <c r="AZ28" s="1">
+      <c r="AZ28" s="2">
         <v>44953</v>
       </c>
       <c r="BA28" t="s">
@@ -19975,7 +20001,7 @@
       <c r="AY29" t="s">
         <v>24</v>
       </c>
-      <c r="AZ29" s="1">
+      <c r="AZ29" s="2">
         <v>44953</v>
       </c>
       <c r="BA29" t="s">
@@ -20085,7 +20111,7 @@
       <c r="AY30" t="s">
         <v>23</v>
       </c>
-      <c r="AZ30" s="1">
+      <c r="AZ30" s="2">
         <v>44960</v>
       </c>
       <c r="BA30" t="s">
@@ -20204,7 +20230,7 @@
       <c r="AY31" t="s">
         <v>24</v>
       </c>
-      <c r="AZ31" s="1">
+      <c r="AZ31" s="2">
         <v>44960</v>
       </c>
       <c r="BA31" t="s">
@@ -20323,7 +20349,7 @@
       <c r="AY32" t="s">
         <v>24</v>
       </c>
-      <c r="AZ32" s="1">
+      <c r="AZ32" s="2">
         <v>44960</v>
       </c>
       <c r="BA32" t="s">
@@ -20442,7 +20468,7 @@
       <c r="AY33" t="s">
         <v>24</v>
       </c>
-      <c r="AZ33" s="1">
+      <c r="AZ33" s="2">
         <v>44960</v>
       </c>
       <c r="BA33" t="s">
@@ -20561,7 +20587,7 @@
       <c r="AY34" t="s">
         <v>24</v>
       </c>
-      <c r="AZ34" s="1">
+      <c r="AZ34" s="2">
         <v>44960</v>
       </c>
       <c r="BA34" t="s">
@@ -20680,7 +20706,7 @@
       <c r="AY35" t="s">
         <v>24</v>
       </c>
-      <c r="AZ35" s="1">
+      <c r="AZ35" s="2">
         <v>44960</v>
       </c>
       <c r="BA35" t="s">
@@ -20799,7 +20825,7 @@
       <c r="AY36" t="s">
         <v>24</v>
       </c>
-      <c r="AZ36" s="1">
+      <c r="AZ36" s="2">
         <v>44960</v>
       </c>
       <c r="BA36" t="s">
@@ -20909,7 +20935,7 @@
       <c r="AY37" t="s">
         <v>23</v>
       </c>
-      <c r="AZ37" s="1">
+      <c r="AZ37" s="2">
         <v>44967</v>
       </c>
       <c r="BA37" t="s">
@@ -21028,7 +21054,7 @@
       <c r="AY38" t="s">
         <v>24</v>
       </c>
-      <c r="AZ38" s="1">
+      <c r="AZ38" s="2">
         <v>44967</v>
       </c>
       <c r="BA38" t="s">
@@ -21147,7 +21173,7 @@
       <c r="AY39" t="s">
         <v>24</v>
       </c>
-      <c r="AZ39" s="1">
+      <c r="AZ39" s="2">
         <v>44967</v>
       </c>
       <c r="BA39" t="s">
@@ -21266,7 +21292,7 @@
       <c r="AY40" t="s">
         <v>24</v>
       </c>
-      <c r="AZ40" s="1">
+      <c r="AZ40" s="2">
         <v>44967</v>
       </c>
       <c r="BA40" t="s">
@@ -21385,7 +21411,7 @@
       <c r="AY41" t="s">
         <v>24</v>
       </c>
-      <c r="AZ41" s="1">
+      <c r="AZ41" s="2">
         <v>44967</v>
       </c>
       <c r="BA41" t="s">
@@ -21504,7 +21530,7 @@
       <c r="AY42" t="s">
         <v>24</v>
       </c>
-      <c r="AZ42" s="1">
+      <c r="AZ42" s="2">
         <v>44967</v>
       </c>
       <c r="BA42" t="s">
@@ -21623,7 +21649,7 @@
       <c r="AY43" t="s">
         <v>24</v>
       </c>
-      <c r="AZ43" s="1">
+      <c r="AZ43" s="2">
         <v>44967</v>
       </c>
       <c r="BA43" t="s">
@@ -21733,7 +21759,7 @@
       <c r="AY44" t="s">
         <v>23</v>
       </c>
-      <c r="AZ44" s="1">
+      <c r="AZ44" s="2">
         <v>44974</v>
       </c>
       <c r="BA44" t="s">
@@ -21852,7 +21878,7 @@
       <c r="AY45" t="s">
         <v>24</v>
       </c>
-      <c r="AZ45" s="1">
+      <c r="AZ45" s="2">
         <v>44974</v>
       </c>
       <c r="BA45" t="s">
@@ -21971,7 +21997,7 @@
       <c r="AY46" t="s">
         <v>24</v>
       </c>
-      <c r="AZ46" s="1">
+      <c r="AZ46" s="2">
         <v>44974</v>
       </c>
       <c r="BA46" t="s">
@@ -22090,7 +22116,7 @@
       <c r="AY47" t="s">
         <v>24</v>
       </c>
-      <c r="AZ47" s="1">
+      <c r="AZ47" s="2">
         <v>44974</v>
       </c>
       <c r="BA47" t="s">
@@ -22209,7 +22235,7 @@
       <c r="AY48" t="s">
         <v>24</v>
       </c>
-      <c r="AZ48" s="1">
+      <c r="AZ48" s="2">
         <v>44974</v>
       </c>
       <c r="BA48" t="s">
@@ -22328,7 +22354,7 @@
       <c r="AY49" t="s">
         <v>24</v>
       </c>
-      <c r="AZ49" s="1">
+      <c r="AZ49" s="2">
         <v>44974</v>
       </c>
       <c r="BA49" t="s">
@@ -22447,7 +22473,7 @@
       <c r="AY50" t="s">
         <v>24</v>
       </c>
-      <c r="AZ50" s="1">
+      <c r="AZ50" s="2">
         <v>44974</v>
       </c>
       <c r="BA50" t="s">
@@ -22557,7 +22583,7 @@
       <c r="AY51" t="s">
         <v>23</v>
       </c>
-      <c r="AZ51" s="1">
+      <c r="AZ51" s="2">
         <v>44981</v>
       </c>
       <c r="BA51" t="s">
@@ -22676,7 +22702,7 @@
       <c r="AY52" t="s">
         <v>24</v>
       </c>
-      <c r="AZ52" s="1">
+      <c r="AZ52" s="2">
         <v>44981</v>
       </c>
       <c r="BA52" t="s">
@@ -22795,7 +22821,7 @@
       <c r="AY53" t="s">
         <v>24</v>
       </c>
-      <c r="AZ53" s="1">
+      <c r="AZ53" s="2">
         <v>44981</v>
       </c>
       <c r="BA53" t="s">
@@ -22914,7 +22940,7 @@
       <c r="AY54" t="s">
         <v>24</v>
       </c>
-      <c r="AZ54" s="1">
+      <c r="AZ54" s="2">
         <v>44981</v>
       </c>
       <c r="BA54" t="s">
@@ -23033,7 +23059,7 @@
       <c r="AY55" t="s">
         <v>24</v>
       </c>
-      <c r="AZ55" s="1">
+      <c r="AZ55" s="2">
         <v>44981</v>
       </c>
       <c r="BA55" t="s">
@@ -23152,7 +23178,7 @@
       <c r="AY56" t="s">
         <v>24</v>
       </c>
-      <c r="AZ56" s="1">
+      <c r="AZ56" s="2">
         <v>44981</v>
       </c>
       <c r="BA56" t="s">
@@ -23271,7 +23297,7 @@
       <c r="AY57" t="s">
         <v>24</v>
       </c>
-      <c r="AZ57" s="1">
+      <c r="AZ57" s="2">
         <v>44981</v>
       </c>
       <c r="BA57" t="s">
@@ -23381,7 +23407,7 @@
       <c r="AY58" t="s">
         <v>23</v>
       </c>
-      <c r="AZ58" s="1">
+      <c r="AZ58" s="2">
         <v>44988</v>
       </c>
       <c r="BA58" t="s">
@@ -23500,7 +23526,7 @@
       <c r="AY59" t="s">
         <v>24</v>
       </c>
-      <c r="AZ59" s="1">
+      <c r="AZ59" s="2">
         <v>44988</v>
       </c>
       <c r="BA59" t="s">
@@ -23619,7 +23645,7 @@
       <c r="AY60" t="s">
         <v>24</v>
       </c>
-      <c r="AZ60" s="1">
+      <c r="AZ60" s="2">
         <v>44988</v>
       </c>
       <c r="BA60" t="s">
@@ -23738,7 +23764,7 @@
       <c r="AY61" t="s">
         <v>24</v>
       </c>
-      <c r="AZ61" s="1">
+      <c r="AZ61" s="2">
         <v>44988</v>
       </c>
       <c r="BA61" t="s">
@@ -23857,7 +23883,7 @@
       <c r="AY62" t="s">
         <v>24</v>
       </c>
-      <c r="AZ62" s="1">
+      <c r="AZ62" s="2">
         <v>44988</v>
       </c>
       <c r="BA62" t="s">
@@ -23976,7 +24002,7 @@
       <c r="AY63" t="s">
         <v>24</v>
       </c>
-      <c r="AZ63" s="1">
+      <c r="AZ63" s="2">
         <v>44988</v>
       </c>
       <c r="BA63" t="s">
@@ -24095,7 +24121,7 @@
       <c r="AY64" t="s">
         <v>24</v>
       </c>
-      <c r="AZ64" s="1">
+      <c r="AZ64" s="2">
         <v>44988</v>
       </c>
       <c r="BA64" t="s">
@@ -24205,7 +24231,7 @@
       <c r="AY65" t="s">
         <v>23</v>
       </c>
-      <c r="AZ65" s="1">
+      <c r="AZ65" s="2">
         <v>45268</v>
       </c>
       <c r="BA65" t="s">
@@ -24324,7 +24350,7 @@
       <c r="AY66" t="s">
         <v>24</v>
       </c>
-      <c r="AZ66" s="1">
+      <c r="AZ66" s="2">
         <v>45268</v>
       </c>
       <c r="BA66" t="s">
@@ -24434,7 +24460,7 @@
       <c r="AY67" t="s">
         <v>23</v>
       </c>
-      <c r="AZ67" s="1">
+      <c r="AZ67" s="2">
         <v>45275</v>
       </c>
       <c r="BA67" t="s">
@@ -24553,7 +24579,7 @@
       <c r="AY68" t="s">
         <v>24</v>
       </c>
-      <c r="AZ68" s="1">
+      <c r="AZ68" s="2">
         <v>45275</v>
       </c>
       <c r="BA68" t="s">
@@ -24672,7 +24698,7 @@
       <c r="AY69" t="s">
         <v>24</v>
       </c>
-      <c r="AZ69" s="1">
+      <c r="AZ69" s="2">
         <v>45275</v>
       </c>
       <c r="BA69" t="s">
@@ -24791,7 +24817,7 @@
       <c r="AY70" t="s">
         <v>24</v>
       </c>
-      <c r="AZ70" s="1">
+      <c r="AZ70" s="2">
         <v>45275</v>
       </c>
       <c r="BA70" t="s">
@@ -24910,7 +24936,7 @@
       <c r="AY71" t="s">
         <v>24</v>
       </c>
-      <c r="AZ71" s="1">
+      <c r="AZ71" s="2">
         <v>45275</v>
       </c>
       <c r="BA71" t="s">
@@ -25020,7 +25046,7 @@
       <c r="AY72" t="s">
         <v>23</v>
       </c>
-      <c r="AZ72" s="1">
+      <c r="AZ72" s="2">
         <v>45282</v>
       </c>
       <c r="BA72" t="s">
@@ -25139,7 +25165,7 @@
       <c r="AY73" t="s">
         <v>24</v>
       </c>
-      <c r="AZ73" s="1">
+      <c r="AZ73" s="2">
         <v>45282</v>
       </c>
       <c r="BA73" t="s">
@@ -25258,7 +25284,7 @@
       <c r="AY74" t="s">
         <v>24</v>
       </c>
-      <c r="AZ74" s="1">
+      <c r="AZ74" s="2">
         <v>45282</v>
       </c>
       <c r="BA74" t="s">
@@ -25377,7 +25403,7 @@
       <c r="AY75" t="s">
         <v>24</v>
       </c>
-      <c r="AZ75" s="1">
+      <c r="AZ75" s="2">
         <v>45282</v>
       </c>
       <c r="BA75" t="s">
@@ -25496,7 +25522,7 @@
       <c r="AY76" t="s">
         <v>24</v>
       </c>
-      <c r="AZ76" s="1">
+      <c r="AZ76" s="2">
         <v>45282</v>
       </c>
       <c r="BA76" t="s">
@@ -25615,7 +25641,7 @@
       <c r="AY77" t="s">
         <v>24</v>
       </c>
-      <c r="AZ77" s="1">
+      <c r="AZ77" s="2">
         <v>45282</v>
       </c>
       <c r="BA77" t="s">
@@ -25734,7 +25760,7 @@
       <c r="AY78" t="s">
         <v>24</v>
       </c>
-      <c r="AZ78" s="1">
+      <c r="AZ78" s="2">
         <v>45282</v>
       </c>
       <c r="BA78" t="s">
@@ -25844,7 +25870,7 @@
       <c r="AY79" t="s">
         <v>23</v>
       </c>
-      <c r="AZ79" s="1">
+      <c r="AZ79" s="2">
         <v>45289</v>
       </c>
       <c r="BA79" t="s">
@@ -25963,7 +25989,7 @@
       <c r="AY80" t="s">
         <v>24</v>
       </c>
-      <c r="AZ80" s="1">
+      <c r="AZ80" s="2">
         <v>45289</v>
       </c>
       <c r="BA80" t="s">
@@ -26082,7 +26108,7 @@
       <c r="AY81" t="s">
         <v>24</v>
       </c>
-      <c r="AZ81" s="1">
+      <c r="AZ81" s="2">
         <v>45289</v>
       </c>
       <c r="BA81" t="s">
@@ -26201,7 +26227,7 @@
       <c r="AY82" t="s">
         <v>24</v>
       </c>
-      <c r="AZ82" s="1">
+      <c r="AZ82" s="2">
         <v>45289</v>
       </c>
       <c r="BA82" t="s">
@@ -26320,7 +26346,7 @@
       <c r="AY83" t="s">
         <v>24</v>
       </c>
-      <c r="AZ83" s="1">
+      <c r="AZ83" s="2">
         <v>45289</v>
       </c>
       <c r="BA83" t="s">
@@ -26439,7 +26465,7 @@
       <c r="AY84" t="s">
         <v>24</v>
       </c>
-      <c r="AZ84" s="1">
+      <c r="AZ84" s="2">
         <v>45289</v>
       </c>
       <c r="BA84" t="s">
@@ -26558,7 +26584,7 @@
       <c r="AY85" t="s">
         <v>24</v>
       </c>
-      <c r="AZ85" s="1">
+      <c r="AZ85" s="2">
         <v>45289</v>
       </c>
       <c r="BA85" t="s">
@@ -26668,7 +26694,7 @@
       <c r="AY86" t="s">
         <v>23</v>
       </c>
-      <c r="AZ86" s="1">
+      <c r="AZ86" s="2">
         <v>45296</v>
       </c>
       <c r="BA86" t="s">
@@ -26787,7 +26813,7 @@
       <c r="AY87" t="s">
         <v>24</v>
       </c>
-      <c r="AZ87" s="1">
+      <c r="AZ87" s="2">
         <v>45296</v>
       </c>
       <c r="BA87" t="s">
@@ -26906,7 +26932,7 @@
       <c r="AY88" t="s">
         <v>24</v>
       </c>
-      <c r="AZ88" s="1">
+      <c r="AZ88" s="2">
         <v>45296</v>
       </c>
       <c r="BA88" t="s">
@@ -27025,7 +27051,7 @@
       <c r="AY89" t="s">
         <v>24</v>
       </c>
-      <c r="AZ89" s="1">
+      <c r="AZ89" s="2">
         <v>45296</v>
       </c>
       <c r="BA89" t="s">
@@ -27144,7 +27170,7 @@
       <c r="AY90" t="s">
         <v>24</v>
       </c>
-      <c r="AZ90" s="1">
+      <c r="AZ90" s="2">
         <v>45296</v>
       </c>
       <c r="BA90" t="s">
@@ -27263,7 +27289,7 @@
       <c r="AY91" t="s">
         <v>24</v>
       </c>
-      <c r="AZ91" s="1">
+      <c r="AZ91" s="2">
         <v>45296</v>
       </c>
       <c r="BA91" t="s">
@@ -27382,7 +27408,7 @@
       <c r="AY92" t="s">
         <v>24</v>
       </c>
-      <c r="AZ92" s="1">
+      <c r="AZ92" s="2">
         <v>45296</v>
       </c>
       <c r="BA92" t="s">
@@ -27492,7 +27518,7 @@
       <c r="AY93" t="s">
         <v>23</v>
       </c>
-      <c r="AZ93" s="1">
+      <c r="AZ93" s="2">
         <v>45303</v>
       </c>
       <c r="BA93" t="s">
@@ -27611,7 +27637,7 @@
       <c r="AY94" t="s">
         <v>24</v>
       </c>
-      <c r="AZ94" s="1">
+      <c r="AZ94" s="2">
         <v>45303</v>
       </c>
       <c r="BA94" t="s">
@@ -27730,7 +27756,7 @@
       <c r="AY95" t="s">
         <v>24</v>
       </c>
-      <c r="AZ95" s="1">
+      <c r="AZ95" s="2">
         <v>45303</v>
       </c>
       <c r="BA95" t="s">
@@ -27849,7 +27875,7 @@
       <c r="AY96" t="s">
         <v>24</v>
       </c>
-      <c r="AZ96" s="1">
+      <c r="AZ96" s="2">
         <v>45303</v>
       </c>
       <c r="BA96" t="s">
@@ -27968,7 +27994,7 @@
       <c r="AY97" t="s">
         <v>24</v>
       </c>
-      <c r="AZ97" s="1">
+      <c r="AZ97" s="2">
         <v>45303</v>
       </c>
       <c r="BA97" t="s">
@@ -28087,7 +28113,7 @@
       <c r="AY98" t="s">
         <v>24</v>
       </c>
-      <c r="AZ98" s="1">
+      <c r="AZ98" s="2">
         <v>45303</v>
       </c>
       <c r="BA98" t="s">
@@ -28206,7 +28232,7 @@
       <c r="AY99" t="s">
         <v>24</v>
       </c>
-      <c r="AZ99" s="1">
+      <c r="AZ99" s="2">
         <v>45303</v>
       </c>
       <c r="BA99" t="s">
@@ -28316,7 +28342,7 @@
       <c r="AY100" t="s">
         <v>23</v>
       </c>
-      <c r="AZ100" s="1">
+      <c r="AZ100" s="2">
         <v>45310</v>
       </c>
       <c r="BA100" t="s">
@@ -28435,7 +28461,7 @@
       <c r="AY101" t="s">
         <v>24</v>
       </c>
-      <c r="AZ101" s="1">
+      <c r="AZ101" s="2">
         <v>45310</v>
       </c>
       <c r="BA101" t="s">
@@ -28554,7 +28580,7 @@
       <c r="AY102" t="s">
         <v>24</v>
       </c>
-      <c r="AZ102" s="1">
+      <c r="AZ102" s="2">
         <v>45310</v>
       </c>
       <c r="BA102" t="s">
@@ -28673,7 +28699,7 @@
       <c r="AY103" t="s">
         <v>24</v>
       </c>
-      <c r="AZ103" s="1">
+      <c r="AZ103" s="2">
         <v>45310</v>
       </c>
       <c r="BA103" t="s">
@@ -28792,7 +28818,7 @@
       <c r="AY104" t="s">
         <v>24</v>
       </c>
-      <c r="AZ104" s="1">
+      <c r="AZ104" s="2">
         <v>45310</v>
       </c>
       <c r="BA104" t="s">
@@ -28911,7 +28937,7 @@
       <c r="AY105" t="s">
         <v>24</v>
       </c>
-      <c r="AZ105" s="1">
+      <c r="AZ105" s="2">
         <v>45310</v>
       </c>
       <c r="BA105" t="s">
@@ -29030,7 +29056,7 @@
       <c r="AY106" t="s">
         <v>24</v>
       </c>
-      <c r="AZ106" s="1">
+      <c r="AZ106" s="2">
         <v>45310</v>
       </c>
       <c r="BA106" t="s">
@@ -29140,7 +29166,7 @@
       <c r="AY107" t="s">
         <v>23</v>
       </c>
-      <c r="AZ107" s="1">
+      <c r="AZ107" s="2">
         <v>45317</v>
       </c>
       <c r="BA107" t="s">
@@ -29259,7 +29285,7 @@
       <c r="AY108" t="s">
         <v>24</v>
       </c>
-      <c r="AZ108" s="1">
+      <c r="AZ108" s="2">
         <v>45317</v>
       </c>
       <c r="BA108" t="s">
@@ -29378,7 +29404,7 @@
       <c r="AY109" t="s">
         <v>24</v>
       </c>
-      <c r="AZ109" s="1">
+      <c r="AZ109" s="2">
         <v>45317</v>
       </c>
       <c r="BA109" t="s">
@@ -29497,7 +29523,7 @@
       <c r="AY110" t="s">
         <v>24</v>
       </c>
-      <c r="AZ110" s="1">
+      <c r="AZ110" s="2">
         <v>45317</v>
       </c>
       <c r="BA110" t="s">
@@ -29616,7 +29642,7 @@
       <c r="AY111" t="s">
         <v>24</v>
       </c>
-      <c r="AZ111" s="1">
+      <c r="AZ111" s="2">
         <v>45317</v>
       </c>
       <c r="BA111" t="s">
@@ -29735,7 +29761,7 @@
       <c r="AY112" t="s">
         <v>24</v>
       </c>
-      <c r="AZ112" s="1">
+      <c r="AZ112" s="2">
         <v>45317</v>
       </c>
       <c r="BA112" t="s">
@@ -29854,7 +29880,7 @@
       <c r="AY113" t="s">
         <v>24</v>
       </c>
-      <c r="AZ113" s="1">
+      <c r="AZ113" s="2">
         <v>45317</v>
       </c>
       <c r="BA113" t="s">
@@ -29964,7 +29990,7 @@
       <c r="AY114" t="s">
         <v>23</v>
       </c>
-      <c r="AZ114" s="1">
+      <c r="AZ114" s="2">
         <v>45324</v>
       </c>
       <c r="BA114" t="s">
@@ -30083,7 +30109,7 @@
       <c r="AY115" t="s">
         <v>24</v>
       </c>
-      <c r="AZ115" s="1">
+      <c r="AZ115" s="2">
         <v>45324</v>
       </c>
       <c r="BA115" t="s">
@@ -30202,7 +30228,7 @@
       <c r="AY116" t="s">
         <v>24</v>
       </c>
-      <c r="AZ116" s="1">
+      <c r="AZ116" s="2">
         <v>45324</v>
       </c>
       <c r="BA116" t="s">
@@ -30321,7 +30347,7 @@
       <c r="AY117" t="s">
         <v>24</v>
       </c>
-      <c r="AZ117" s="1">
+      <c r="AZ117" s="2">
         <v>45324</v>
       </c>
       <c r="BA117" t="s">
@@ -30440,7 +30466,7 @@
       <c r="AY118" t="s">
         <v>24</v>
       </c>
-      <c r="AZ118" s="1">
+      <c r="AZ118" s="2">
         <v>45324</v>
       </c>
       <c r="BA118" t="s">
@@ -30559,7 +30585,7 @@
       <c r="AY119" t="s">
         <v>24</v>
       </c>
-      <c r="AZ119" s="1">
+      <c r="AZ119" s="2">
         <v>45324</v>
       </c>
       <c r="BA119" t="s">
@@ -30678,7 +30704,7 @@
       <c r="AY120" t="s">
         <v>24</v>
       </c>
-      <c r="AZ120" s="1">
+      <c r="AZ120" s="2">
         <v>45324</v>
       </c>
       <c r="BA120" t="s">
@@ -30788,7 +30814,7 @@
       <c r="AY121" t="s">
         <v>23</v>
       </c>
-      <c r="AZ121" s="1">
+      <c r="AZ121" s="2">
         <v>45331</v>
       </c>
       <c r="BA121" t="s">
@@ -30907,7 +30933,7 @@
       <c r="AY122" t="s">
         <v>24</v>
       </c>
-      <c r="AZ122" s="1">
+      <c r="AZ122" s="2">
         <v>45331</v>
       </c>
       <c r="BA122" t="s">
@@ -31026,7 +31052,7 @@
       <c r="AY123" t="s">
         <v>24</v>
       </c>
-      <c r="AZ123" s="1">
+      <c r="AZ123" s="2">
         <v>45331</v>
       </c>
       <c r="BA123" t="s">
@@ -31145,7 +31171,7 @@
       <c r="AY124" t="s">
         <v>24</v>
       </c>
-      <c r="AZ124" s="1">
+      <c r="AZ124" s="2">
         <v>45331</v>
       </c>
       <c r="BA124" t="s">
@@ -31264,7 +31290,7 @@
       <c r="AY125" t="s">
         <v>24</v>
       </c>
-      <c r="AZ125" s="1">
+      <c r="AZ125" s="2">
         <v>45331</v>
       </c>
       <c r="BA125" t="s">
@@ -31383,7 +31409,7 @@
       <c r="AY126" t="s">
         <v>24</v>
       </c>
-      <c r="AZ126" s="1">
+      <c r="AZ126" s="2">
         <v>45331</v>
       </c>
       <c r="BA126" t="s">
@@ -31502,7 +31528,7 @@
       <c r="AY127" t="s">
         <v>24</v>
       </c>
-      <c r="AZ127" s="1">
+      <c r="AZ127" s="2">
         <v>45331</v>
       </c>
       <c r="BA127" t="s">
@@ -31612,7 +31638,7 @@
       <c r="AY128" t="s">
         <v>23</v>
       </c>
-      <c r="AZ128" s="1">
+      <c r="AZ128" s="2">
         <v>45338</v>
       </c>
       <c r="BA128" t="s">
@@ -31731,7 +31757,7 @@
       <c r="AY129" t="s">
         <v>24</v>
       </c>
-      <c r="AZ129" s="1">
+      <c r="AZ129" s="2">
         <v>45338</v>
       </c>
       <c r="BA129" t="s">
@@ -31850,7 +31876,7 @@
       <c r="AY130" t="s">
         <v>24</v>
       </c>
-      <c r="AZ130" s="1">
+      <c r="AZ130" s="2">
         <v>45338</v>
       </c>
       <c r="BA130" t="s">
@@ -31969,7 +31995,7 @@
       <c r="AY131" t="s">
         <v>24</v>
       </c>
-      <c r="AZ131" s="1">
+      <c r="AZ131" s="2">
         <v>45338</v>
       </c>
       <c r="BA131" t="s">
@@ -32088,7 +32114,7 @@
       <c r="AY132" t="s">
         <v>24</v>
       </c>
-      <c r="AZ132" s="1">
+      <c r="AZ132" s="2">
         <v>45338</v>
       </c>
       <c r="BA132" t="s">
@@ -32207,7 +32233,7 @@
       <c r="AY133" t="s">
         <v>24</v>
       </c>
-      <c r="AZ133" s="1">
+      <c r="AZ133" s="2">
         <v>45338</v>
       </c>
       <c r="BA133" t="s">
@@ -32326,7 +32352,7 @@
       <c r="AY134" t="s">
         <v>24</v>
       </c>
-      <c r="AZ134" s="1">
+      <c r="AZ134" s="2">
         <v>45338</v>
       </c>
       <c r="BA134" t="s">
@@ -32436,7 +32462,7 @@
       <c r="AY135" t="s">
         <v>23</v>
       </c>
-      <c r="AZ135" s="1">
+      <c r="AZ135" s="2">
         <v>45345</v>
       </c>
       <c r="BA135" t="s">
@@ -32555,7 +32581,7 @@
       <c r="AY136" t="s">
         <v>24</v>
       </c>
-      <c r="AZ136" s="1">
+      <c r="AZ136" s="2">
         <v>45345</v>
       </c>
       <c r="BA136" t="s">
@@ -32674,7 +32700,7 @@
       <c r="AY137" t="s">
         <v>24</v>
       </c>
-      <c r="AZ137" s="1">
+      <c r="AZ137" s="2">
         <v>45345</v>
       </c>
       <c r="BA137" t="s">
@@ -32793,7 +32819,7 @@
       <c r="AY138" t="s">
         <v>24</v>
       </c>
-      <c r="AZ138" s="1">
+      <c r="AZ138" s="2">
         <v>45345</v>
       </c>
       <c r="BA138" t="s">
@@ -32912,7 +32938,7 @@
       <c r="AY139" t="s">
         <v>24</v>
       </c>
-      <c r="AZ139" s="1">
+      <c r="AZ139" s="2">
         <v>45345</v>
       </c>
       <c r="BA139" t="s">
@@ -33031,7 +33057,7 @@
       <c r="AY140" t="s">
         <v>24</v>
       </c>
-      <c r="AZ140" s="1">
+      <c r="AZ140" s="2">
         <v>45345</v>
       </c>
       <c r="BA140" t="s">
@@ -33150,7 +33176,7 @@
       <c r="AY141" t="s">
         <v>24</v>
       </c>
-      <c r="AZ141" s="1">
+      <c r="AZ141" s="2">
         <v>45345</v>
       </c>
       <c r="BA141" t="s">
@@ -33260,7 +33286,7 @@
       <c r="AY142" t="s">
         <v>23</v>
       </c>
-      <c r="AZ142" s="1">
+      <c r="AZ142" s="2">
         <v>45639</v>
       </c>
       <c r="BA142" t="s">
@@ -33379,7 +33405,7 @@
       <c r="AY143" t="s">
         <v>24</v>
       </c>
-      <c r="AZ143" s="1">
+      <c r="AZ143" s="2">
         <v>45639</v>
       </c>
       <c r="BA143" t="s">
@@ -33489,7 +33515,7 @@
       <c r="AY144" t="s">
         <v>23</v>
       </c>
-      <c r="AZ144" s="1">
+      <c r="AZ144" s="2">
         <v>45646</v>
       </c>
       <c r="BA144" t="s">
@@ -33608,7 +33634,7 @@
       <c r="AY145" t="s">
         <v>24</v>
       </c>
-      <c r="AZ145" s="1">
+      <c r="AZ145" s="2">
         <v>45646</v>
       </c>
       <c r="BA145" t="s">
@@ -33727,7 +33753,7 @@
       <c r="AY146" t="s">
         <v>24</v>
       </c>
-      <c r="AZ146" s="1">
+      <c r="AZ146" s="2">
         <v>45646</v>
       </c>
       <c r="BA146" t="s">
@@ -33846,7 +33872,7 @@
       <c r="AY147" t="s">
         <v>24</v>
       </c>
-      <c r="AZ147" s="1">
+      <c r="AZ147" s="2">
         <v>45646</v>
       </c>
       <c r="BA147" t="s">
@@ -33965,7 +33991,7 @@
       <c r="AY148" t="s">
         <v>24</v>
       </c>
-      <c r="AZ148" s="1">
+      <c r="AZ148" s="2">
         <v>45646</v>
       </c>
       <c r="BA148" t="s">
@@ -34084,7 +34110,7 @@
       <c r="AY149" t="s">
         <v>24</v>
       </c>
-      <c r="AZ149" s="1">
+      <c r="AZ149" s="2">
         <v>45646</v>
       </c>
       <c r="BA149" t="s">
@@ -34203,7 +34229,7 @@
       <c r="AY150" t="s">
         <v>24</v>
       </c>
-      <c r="AZ150" s="1">
+      <c r="AZ150" s="2">
         <v>45646</v>
       </c>
       <c r="BA150" t="s">
@@ -34313,7 +34339,7 @@
       <c r="AY151" t="s">
         <v>23</v>
       </c>
-      <c r="AZ151" s="1">
+      <c r="AZ151" s="2">
         <v>45653</v>
       </c>
       <c r="BA151" t="s">
@@ -34432,7 +34458,7 @@
       <c r="AY152" t="s">
         <v>24</v>
       </c>
-      <c r="AZ152" s="1">
+      <c r="AZ152" s="2">
         <v>45653</v>
       </c>
       <c r="BA152" t="s">
@@ -34551,7 +34577,7 @@
       <c r="AY153" t="s">
         <v>24</v>
       </c>
-      <c r="AZ153" s="1">
+      <c r="AZ153" s="2">
         <v>45653</v>
       </c>
       <c r="BA153" t="s">
@@ -34670,7 +34696,7 @@
       <c r="AY154" t="s">
         <v>24</v>
       </c>
-      <c r="AZ154" s="1">
+      <c r="AZ154" s="2">
         <v>45653</v>
       </c>
       <c r="BA154" t="s">
@@ -34789,7 +34815,7 @@
       <c r="AY155" t="s">
         <v>24</v>
       </c>
-      <c r="AZ155" s="1">
+      <c r="AZ155" s="2">
         <v>45653</v>
       </c>
       <c r="BA155" t="s">
@@ -34908,7 +34934,7 @@
       <c r="AY156" t="s">
         <v>24</v>
       </c>
-      <c r="AZ156" s="1">
+      <c r="AZ156" s="2">
         <v>45653</v>
       </c>
       <c r="BA156" t="s">
@@ -35027,7 +35053,7 @@
       <c r="AY157" t="s">
         <v>24</v>
       </c>
-      <c r="AZ157" s="1">
+      <c r="AZ157" s="2">
         <v>45653</v>
       </c>
       <c r="BA157" t="s">
@@ -35137,7 +35163,7 @@
       <c r="AY158" t="s">
         <v>23</v>
       </c>
-      <c r="AZ158" s="1">
+      <c r="AZ158" s="2">
         <v>45660</v>
       </c>
       <c r="BA158" t="s">
@@ -35256,7 +35282,7 @@
       <c r="AY159" t="s">
         <v>24</v>
       </c>
-      <c r="AZ159" s="1">
+      <c r="AZ159" s="2">
         <v>45660</v>
       </c>
       <c r="BA159" t="s">
@@ -35375,7 +35401,7 @@
       <c r="AY160" t="s">
         <v>24</v>
       </c>
-      <c r="AZ160" s="1">
+      <c r="AZ160" s="2">
         <v>45660</v>
       </c>
       <c r="BA160" t="s">
@@ -35494,7 +35520,7 @@
       <c r="AY161" t="s">
         <v>24</v>
       </c>
-      <c r="AZ161" s="1">
+      <c r="AZ161" s="2">
         <v>45660</v>
       </c>
       <c r="BA161" t="s">
@@ -35613,7 +35639,7 @@
       <c r="AY162" t="s">
         <v>24</v>
       </c>
-      <c r="AZ162" s="1">
+      <c r="AZ162" s="2">
         <v>45660</v>
       </c>
       <c r="BA162" t="s">
@@ -35732,7 +35758,7 @@
       <c r="AY163" t="s">
         <v>24</v>
       </c>
-      <c r="AZ163" s="1">
+      <c r="AZ163" s="2">
         <v>45660</v>
       </c>
       <c r="BA163" t="s">
@@ -35851,7 +35877,7 @@
       <c r="AY164" t="s">
         <v>24</v>
       </c>
-      <c r="AZ164" s="1">
+      <c r="AZ164" s="2">
         <v>45660</v>
       </c>
       <c r="BA164" t="s">
@@ -35961,7 +35987,7 @@
       <c r="AY165" t="s">
         <v>23</v>
       </c>
-      <c r="AZ165" s="1">
+      <c r="AZ165" s="2">
         <v>45667</v>
       </c>
       <c r="BA165" t="s">
@@ -36080,7 +36106,7 @@
       <c r="AY166" t="s">
         <v>24</v>
       </c>
-      <c r="AZ166" s="1">
+      <c r="AZ166" s="2">
         <v>45667</v>
       </c>
       <c r="BA166" t="s">
@@ -36199,7 +36225,7 @@
       <c r="AY167" t="s">
         <v>24</v>
       </c>
-      <c r="AZ167" s="1">
+      <c r="AZ167" s="2">
         <v>45667</v>
       </c>
       <c r="BA167" t="s">
@@ -36318,7 +36344,7 @@
       <c r="AY168" t="s">
         <v>24</v>
       </c>
-      <c r="AZ168" s="1">
+      <c r="AZ168" s="2">
         <v>45667</v>
       </c>
       <c r="BA168" t="s">
@@ -36437,7 +36463,7 @@
       <c r="AY169" t="s">
         <v>24</v>
       </c>
-      <c r="AZ169" s="1">
+      <c r="AZ169" s="2">
         <v>45667</v>
       </c>
       <c r="BA169" t="s">
@@ -36556,7 +36582,7 @@
       <c r="AY170" t="s">
         <v>24</v>
       </c>
-      <c r="AZ170" s="1">
+      <c r="AZ170" s="2">
         <v>45667</v>
       </c>
       <c r="BA170" t="s">
@@ -36675,7 +36701,7 @@
       <c r="AY171" t="s">
         <v>24</v>
       </c>
-      <c r="AZ171" s="1">
+      <c r="AZ171" s="2">
         <v>45667</v>
       </c>
       <c r="BA171" t="s">
@@ -36785,7 +36811,7 @@
       <c r="AY172" t="s">
         <v>23</v>
       </c>
-      <c r="AZ172" s="1">
+      <c r="AZ172" s="2">
         <v>45674</v>
       </c>
       <c r="BA172" t="s">
@@ -36904,7 +36930,7 @@
       <c r="AY173" t="s">
         <v>24</v>
       </c>
-      <c r="AZ173" s="1">
+      <c r="AZ173" s="2">
         <v>45674</v>
       </c>
       <c r="BA173" t="s">
@@ -37023,7 +37049,7 @@
       <c r="AY174" t="s">
         <v>24</v>
       </c>
-      <c r="AZ174" s="1">
+      <c r="AZ174" s="2">
         <v>45674</v>
       </c>
       <c r="BA174" t="s">
@@ -37142,7 +37168,7 @@
       <c r="AY175" t="s">
         <v>24</v>
       </c>
-      <c r="AZ175" s="1">
+      <c r="AZ175" s="2">
         <v>45674</v>
       </c>
       <c r="BA175" t="s">
@@ -37261,7 +37287,7 @@
       <c r="AY176" t="s">
         <v>24</v>
       </c>
-      <c r="AZ176" s="1">
+      <c r="AZ176" s="2">
         <v>45674</v>
       </c>
       <c r="BA176" t="s">
@@ -37380,7 +37406,7 @@
       <c r="AY177" t="s">
         <v>24</v>
       </c>
-      <c r="AZ177" s="1">
+      <c r="AZ177" s="2">
         <v>45674</v>
       </c>
       <c r="BA177" t="s">
@@ -37499,7 +37525,7 @@
       <c r="AY178" t="s">
         <v>24</v>
       </c>
-      <c r="AZ178" s="1">
+      <c r="AZ178" s="2">
         <v>45674</v>
       </c>
       <c r="BA178" t="s">
@@ -37609,7 +37635,7 @@
       <c r="AY179" t="s">
         <v>23</v>
       </c>
-      <c r="AZ179" s="1">
+      <c r="AZ179" s="2">
         <v>45681</v>
       </c>
       <c r="BA179" t="s">
@@ -37728,7 +37754,7 @@
       <c r="AY180" t="s">
         <v>24</v>
       </c>
-      <c r="AZ180" s="1">
+      <c r="AZ180" s="2">
         <v>45681</v>
       </c>
       <c r="BA180" t="s">
@@ -37847,7 +37873,7 @@
       <c r="AY181" t="s">
         <v>24</v>
       </c>
-      <c r="AZ181" s="1">
+      <c r="AZ181" s="2">
         <v>45681</v>
       </c>
       <c r="BA181" t="s">
@@ -37966,7 +37992,7 @@
       <c r="AY182" t="s">
         <v>24</v>
       </c>
-      <c r="AZ182" s="1">
+      <c r="AZ182" s="2">
         <v>45681</v>
       </c>
       <c r="BA182" t="s">
@@ -38085,7 +38111,7 @@
       <c r="AY183" t="s">
         <v>24</v>
       </c>
-      <c r="AZ183" s="1">
+      <c r="AZ183" s="2">
         <v>45681</v>
       </c>
       <c r="BA183" t="s">
@@ -38204,7 +38230,7 @@
       <c r="AY184" t="s">
         <v>24</v>
       </c>
-      <c r="AZ184" s="1">
+      <c r="AZ184" s="2">
         <v>45681</v>
       </c>
       <c r="BA184" t="s">
@@ -38323,7 +38349,7 @@
       <c r="AY185" t="s">
         <v>24</v>
       </c>
-      <c r="AZ185" s="1">
+      <c r="AZ185" s="2">
         <v>45681</v>
       </c>
       <c r="BA185" t="s">
@@ -38433,7 +38459,7 @@
       <c r="AY186" t="s">
         <v>23</v>
       </c>
-      <c r="AZ186" s="1">
+      <c r="AZ186" s="2">
         <v>45688</v>
       </c>
       <c r="BA186" t="s">
@@ -38552,7 +38578,7 @@
       <c r="AY187" t="s">
         <v>24</v>
       </c>
-      <c r="AZ187" s="1">
+      <c r="AZ187" s="2">
         <v>45688</v>
       </c>
       <c r="BA187" t="s">
@@ -38671,7 +38697,7 @@
       <c r="AY188" t="s">
         <v>24</v>
       </c>
-      <c r="AZ188" s="1">
+      <c r="AZ188" s="2">
         <v>45688</v>
       </c>
       <c r="BA188" t="s">
@@ -38790,7 +38816,7 @@
       <c r="AY189" t="s">
         <v>24</v>
       </c>
-      <c r="AZ189" s="1">
+      <c r="AZ189" s="2">
         <v>45688</v>
       </c>
       <c r="BA189" t="s">
@@ -38909,7 +38935,7 @@
       <c r="AY190" t="s">
         <v>24</v>
       </c>
-      <c r="AZ190" s="1">
+      <c r="AZ190" s="2">
         <v>45688</v>
       </c>
       <c r="BA190" t="s">
@@ -39028,7 +39054,7 @@
       <c r="AY191" t="s">
         <v>24</v>
       </c>
-      <c r="AZ191" s="1">
+      <c r="AZ191" s="2">
         <v>45688</v>
       </c>
       <c r="BA191" t="s">
@@ -39147,7 +39173,7 @@
       <c r="AY192" t="s">
         <v>24</v>
       </c>
-      <c r="AZ192" s="1">
+      <c r="AZ192" s="2">
         <v>45688</v>
       </c>
       <c r="BA192" t="s">
@@ -39257,7 +39283,7 @@
       <c r="AY193" t="s">
         <v>23</v>
       </c>
-      <c r="AZ193" s="1">
+      <c r="AZ193" s="2">
         <v>45695</v>
       </c>
       <c r="BA193" t="s">
@@ -39376,7 +39402,7 @@
       <c r="AY194" t="s">
         <v>24</v>
       </c>
-      <c r="AZ194" s="1">
+      <c r="AZ194" s="2">
         <v>45695</v>
       </c>
       <c r="BA194" t="s">
@@ -39495,7 +39521,7 @@
       <c r="AY195" t="s">
         <v>24</v>
       </c>
-      <c r="AZ195" s="1">
+      <c r="AZ195" s="2">
         <v>45695</v>
       </c>
       <c r="BA195" t="s">
@@ -39614,7 +39640,7 @@
       <c r="AY196" t="s">
         <v>24</v>
       </c>
-      <c r="AZ196" s="1">
+      <c r="AZ196" s="2">
         <v>45695</v>
       </c>
       <c r="BA196" t="s">
@@ -39733,7 +39759,7 @@
       <c r="AY197" t="s">
         <v>24</v>
       </c>
-      <c r="AZ197" s="1">
+      <c r="AZ197" s="2">
         <v>45695</v>
       </c>
       <c r="BA197" t="s">
@@ -39852,7 +39878,7 @@
       <c r="AY198" t="s">
         <v>24</v>
       </c>
-      <c r="AZ198" s="1">
+      <c r="AZ198" s="2">
         <v>45695</v>
       </c>
       <c r="BA198" t="s">
@@ -39971,7 +39997,7 @@
       <c r="AY199" t="s">
         <v>24</v>
       </c>
-      <c r="AZ199" s="1">
+      <c r="AZ199" s="2">
         <v>45695</v>
       </c>
       <c r="BA199" t="s">
@@ -40081,7 +40107,7 @@
       <c r="AY200" t="s">
         <v>23</v>
       </c>
-      <c r="AZ200" s="1">
+      <c r="AZ200" s="2">
         <v>45702</v>
       </c>
       <c r="BA200" t="s">
@@ -40200,7 +40226,7 @@
       <c r="AY201" t="s">
         <v>24</v>
       </c>
-      <c r="AZ201" s="1">
+      <c r="AZ201" s="2">
         <v>45702</v>
       </c>
       <c r="BA201" t="s">
@@ -40319,7 +40345,7 @@
       <c r="AY202" t="s">
         <v>24</v>
       </c>
-      <c r="AZ202" s="1">
+      <c r="AZ202" s="2">
         <v>45702</v>
       </c>
       <c r="BA202" t="s">
@@ -40438,7 +40464,7 @@
       <c r="AY203" t="s">
         <v>24</v>
       </c>
-      <c r="AZ203" s="1">
+      <c r="AZ203" s="2">
         <v>45702</v>
       </c>
       <c r="BA203" t="s">
@@ -40557,7 +40583,7 @@
       <c r="AY204" t="s">
         <v>24</v>
       </c>
-      <c r="AZ204" s="1">
+      <c r="AZ204" s="2">
         <v>45702</v>
       </c>
       <c r="BA204" t="s">
@@ -40676,7 +40702,7 @@
       <c r="AY205" t="s">
         <v>24</v>
       </c>
-      <c r="AZ205" s="1">
+      <c r="AZ205" s="2">
         <v>45702</v>
       </c>
       <c r="BA205" t="s">
@@ -40795,7 +40821,7 @@
       <c r="AY206" t="s">
         <v>24</v>
       </c>
-      <c r="AZ206" s="1">
+      <c r="AZ206" s="2">
         <v>45702</v>
       </c>
       <c r="BA206" t="s">
@@ -40905,7 +40931,7 @@
       <c r="AY207" t="s">
         <v>23</v>
       </c>
-      <c r="AZ207" s="1">
+      <c r="AZ207" s="2">
         <v>45709</v>
       </c>
       <c r="BA207" t="s">
@@ -41024,7 +41050,7 @@
       <c r="AY208" t="s">
         <v>24</v>
       </c>
-      <c r="AZ208" s="1">
+      <c r="AZ208" s="2">
         <v>45709</v>
       </c>
       <c r="BA208" t="s">
@@ -41143,7 +41169,7 @@
       <c r="AY209" t="s">
         <v>24</v>
       </c>
-      <c r="AZ209" s="1">
+      <c r="AZ209" s="2">
         <v>45709</v>
       </c>
       <c r="BA209" t="s">
@@ -41262,7 +41288,7 @@
       <c r="AY210" t="s">
         <v>24</v>
       </c>
-      <c r="AZ210" s="1">
+      <c r="AZ210" s="2">
         <v>45709</v>
       </c>
       <c r="BA210" t="s">
@@ -41381,7 +41407,7 @@
       <c r="AY211" t="s">
         <v>24</v>
       </c>
-      <c r="AZ211" s="1">
+      <c r="AZ211" s="2">
         <v>45709</v>
       </c>
       <c r="BA211" t="s">
@@ -41500,7 +41526,7 @@
       <c r="AY212" t="s">
         <v>24</v>
       </c>
-      <c r="AZ212" s="1">
+      <c r="AZ212" s="2">
         <v>45709</v>
       </c>
       <c r="BA212" t="s">
@@ -41619,7 +41645,7 @@
       <c r="AY213" t="s">
         <v>24</v>
       </c>
-      <c r="AZ213" s="1">
+      <c r="AZ213" s="2">
         <v>45709</v>
       </c>
       <c r="BA213" t="s">
@@ -41729,7 +41755,7 @@
       <c r="AY214" t="s">
         <v>23</v>
       </c>
-      <c r="AZ214" s="1">
+      <c r="AZ214" s="2">
         <v>45716</v>
       </c>
       <c r="BA214" t="s">
@@ -41848,7 +41874,7 @@
       <c r="AY215" t="s">
         <v>24</v>
       </c>
-      <c r="AZ215" s="1">
+      <c r="AZ215" s="2">
         <v>45716</v>
       </c>
       <c r="BA215" t="s">
@@ -41967,7 +41993,7 @@
       <c r="AY216" t="s">
         <v>24</v>
       </c>
-      <c r="AZ216" s="1">
+      <c r="AZ216" s="2">
         <v>45716</v>
       </c>
       <c r="BA216" t="s">
@@ -42086,7 +42112,7 @@
       <c r="AY217" t="s">
         <v>24</v>
       </c>
-      <c r="AZ217" s="1">
+      <c r="AZ217" s="2">
         <v>45716</v>
       </c>
       <c r="BA217" t="s">
@@ -42205,7 +42231,7 @@
       <c r="AY218" t="s">
         <v>24</v>
       </c>
-      <c r="AZ218" s="1">
+      <c r="AZ218" s="2">
         <v>45716</v>
       </c>
       <c r="BA218" t="s">
@@ -42324,7 +42350,7 @@
       <c r="AY219" t="s">
         <v>24</v>
       </c>
-      <c r="AZ219" s="1">
+      <c r="AZ219" s="2">
         <v>45716</v>
       </c>
       <c r="BA219" t="s">
@@ -42443,7 +42469,7 @@
       <c r="AY220" t="s">
         <v>24</v>
       </c>
-      <c r="AZ220" s="1">
+      <c r="AZ220" s="2">
         <v>45716</v>
       </c>
       <c r="BA220" t="s">
@@ -42553,7 +42579,7 @@
       <c r="AY221" t="s">
         <v>23</v>
       </c>
-      <c r="AZ221" s="1">
+      <c r="AZ221" s="2">
         <v>46003</v>
       </c>
       <c r="BA221" t="s">
@@ -42672,7 +42698,7 @@
       <c r="AY222" t="s">
         <v>24</v>
       </c>
-      <c r="AZ222" s="1">
+      <c r="AZ222" s="2">
         <v>46003</v>
       </c>
       <c r="BA222" t="s">
@@ -42791,7 +42817,7 @@
       <c r="AY223" t="s">
         <v>24</v>
       </c>
-      <c r="AZ223" s="1">
+      <c r="AZ223" s="2">
         <v>46003</v>
       </c>
       <c r="BA223" t="s">
@@ -42910,7 +42936,7 @@
       <c r="AY224" t="s">
         <v>24</v>
       </c>
-      <c r="AZ224" s="1">
+      <c r="AZ224" s="2">
         <v>46003</v>
       </c>
       <c r="BA224" t="s">
@@ -43029,7 +43055,7 @@
       <c r="AY225" t="s">
         <v>24</v>
       </c>
-      <c r="AZ225" s="1">
+      <c r="AZ225" s="2">
         <v>46003</v>
       </c>
       <c r="BA225" t="s">
@@ -43148,7 +43174,7 @@
       <c r="AY226" t="s">
         <v>24</v>
       </c>
-      <c r="AZ226" s="1">
+      <c r="AZ226" s="2">
         <v>46003</v>
       </c>
       <c r="BA226" t="s">
@@ -43267,7 +43293,7 @@
       <c r="AY227" t="s">
         <v>24</v>
       </c>
-      <c r="AZ227" s="1">
+      <c r="AZ227" s="2">
         <v>46003</v>
       </c>
       <c r="BA227" t="s">
@@ -43377,7 +43403,7 @@
       <c r="AY228" t="s">
         <v>23</v>
       </c>
-      <c r="AZ228" s="1">
+      <c r="AZ228" s="2">
         <v>46010</v>
       </c>
       <c r="BA228" t="s">
@@ -43496,7 +43522,7 @@
       <c r="AY229" t="s">
         <v>24</v>
       </c>
-      <c r="AZ229" s="1">
+      <c r="AZ229" s="2">
         <v>46010</v>
       </c>
       <c r="BA229" t="s">
@@ -43612,7 +43638,7 @@
       <c r="AY230" t="s">
         <v>24</v>
       </c>
-      <c r="AZ230" s="1">
+      <c r="AZ230" s="2">
         <v>46010</v>
       </c>
       <c r="BA230" t="s">
@@ -43728,7 +43754,7 @@
       <c r="AY231" t="s">
         <v>24</v>
       </c>
-      <c r="AZ231" s="1">
+      <c r="AZ231" s="2">
         <v>46010</v>
       </c>
       <c r="BA231" t="s">
@@ -43844,7 +43870,7 @@
       <c r="AY232" t="s">
         <v>24</v>
       </c>
-      <c r="AZ232" s="1">
+      <c r="AZ232" s="2">
         <v>46010</v>
       </c>
       <c r="BA232" t="s">
@@ -43960,7 +43986,7 @@
       <c r="AY233" t="s">
         <v>24</v>
       </c>
-      <c r="AZ233" s="1">
+      <c r="AZ233" s="2">
         <v>46010</v>
       </c>
       <c r="BA233" t="s">
@@ -44076,7 +44102,7 @@
       <c r="AY234" t="s">
         <v>24</v>
       </c>
-      <c r="AZ234" s="1">
+      <c r="AZ234" s="2">
         <v>46010</v>
       </c>
       <c r="BA234" t="s">
@@ -44186,7 +44212,7 @@
       <c r="AY235" t="s">
         <v>23</v>
       </c>
-      <c r="AZ235" s="1">
+      <c r="AZ235" s="2">
         <v>46017</v>
       </c>
       <c r="BA235" t="s">
@@ -44305,7 +44331,7 @@
       <c r="AY236" t="s">
         <v>24</v>
       </c>
-      <c r="AZ236" s="1">
+      <c r="AZ236" s="2">
         <v>46017</v>
       </c>
       <c r="BA236" t="s">
@@ -44424,7 +44450,7 @@
       <c r="AY237" t="s">
         <v>24</v>
       </c>
-      <c r="AZ237" s="1">
+      <c r="AZ237" s="2">
         <v>46017</v>
       </c>
       <c r="BA237" t="s">
@@ -44543,7 +44569,7 @@
       <c r="AY238" t="s">
         <v>24</v>
       </c>
-      <c r="AZ238" s="1">
+      <c r="AZ238" s="2">
         <v>46017</v>
       </c>
       <c r="BA238" t="s">
@@ -44662,7 +44688,7 @@
       <c r="AY239" t="s">
         <v>24</v>
       </c>
-      <c r="AZ239" s="1">
+      <c r="AZ239" s="2">
         <v>46017</v>
       </c>
       <c r="BA239" t="s">
@@ -44781,7 +44807,7 @@
       <c r="AY240" t="s">
         <v>24</v>
       </c>
-      <c r="AZ240" s="1">
+      <c r="AZ240" s="2">
         <v>46017</v>
       </c>
       <c r="BA240" t="s">
@@ -44900,7 +44926,7 @@
       <c r="AY241" t="s">
         <v>24</v>
       </c>
-      <c r="AZ241" s="1">
+      <c r="AZ241" s="2">
         <v>46017</v>
       </c>
       <c r="BA241" t="s">
@@ -45010,7 +45036,7 @@
       <c r="AY242" t="s">
         <v>23</v>
       </c>
-      <c r="AZ242" s="1">
+      <c r="AZ242" s="2">
         <v>46024</v>
       </c>
       <c r="BA242" t="s">
@@ -45129,7 +45155,7 @@
       <c r="AY243" t="s">
         <v>24</v>
       </c>
-      <c r="AZ243" s="1">
+      <c r="AZ243" s="2">
         <v>46024</v>
       </c>
       <c r="BA243" t="s">
@@ -45248,7 +45274,7 @@
       <c r="AY244" t="s">
         <v>24</v>
       </c>
-      <c r="AZ244" s="1">
+      <c r="AZ244" s="2">
         <v>46024</v>
       </c>
       <c r="BA244" t="s">
@@ -45367,7 +45393,7 @@
       <c r="AY245" t="s">
         <v>24</v>
       </c>
-      <c r="AZ245" s="1">
+      <c r="AZ245" s="2">
         <v>46024</v>
       </c>
       <c r="BA245" t="s">
@@ -45486,7 +45512,7 @@
       <c r="AY246" t="s">
         <v>24</v>
       </c>
-      <c r="AZ246" s="1">
+      <c r="AZ246" s="2">
         <v>46024</v>
       </c>
       <c r="BA246" t="s">
@@ -45605,7 +45631,7 @@
       <c r="AY247" t="s">
         <v>24</v>
       </c>
-      <c r="AZ247" s="1">
+      <c r="AZ247" s="2">
         <v>46024</v>
       </c>
       <c r="BA247" t="s">
@@ -45724,7 +45750,7 @@
       <c r="AY248" t="s">
         <v>24</v>
       </c>
-      <c r="AZ248" s="1">
+      <c r="AZ248" s="2">
         <v>46024</v>
       </c>
       <c r="BA248" t="s">
@@ -45834,7 +45860,7 @@
       <c r="AY249" t="s">
         <v>23</v>
       </c>
-      <c r="AZ249" s="1">
+      <c r="AZ249" s="2">
         <v>46031</v>
       </c>
       <c r="BA249" t="s">
@@ -45953,7 +45979,7 @@
       <c r="AY250" t="s">
         <v>24</v>
       </c>
-      <c r="AZ250" s="1">
+      <c r="AZ250" s="2">
         <v>46031</v>
       </c>
       <c r="BA250" t="s">
@@ -46072,7 +46098,7 @@
       <c r="AY251" t="s">
         <v>24</v>
       </c>
-      <c r="AZ251" s="1">
+      <c r="AZ251" s="2">
         <v>46031</v>
       </c>
       <c r="BA251" t="s">
@@ -46191,7 +46217,7 @@
       <c r="AY252" t="s">
         <v>24</v>
       </c>
-      <c r="AZ252" s="1">
+      <c r="AZ252" s="2">
         <v>46031</v>
       </c>
       <c r="BA252" t="s">
@@ -46310,7 +46336,7 @@
       <c r="AY253" t="s">
         <v>24</v>
       </c>
-      <c r="AZ253" s="1">
+      <c r="AZ253" s="2">
         <v>46031</v>
       </c>
       <c r="BA253" t="s">
@@ -46429,7 +46455,7 @@
       <c r="AY254" t="s">
         <v>24</v>
       </c>
-      <c r="AZ254" s="1">
+      <c r="AZ254" s="2">
         <v>46031</v>
       </c>
       <c r="BA254" t="s">
@@ -46548,7 +46574,7 @@
       <c r="AY255" t="s">
         <v>24</v>
       </c>
-      <c r="AZ255" s="1">
+      <c r="AZ255" s="2">
         <v>46031</v>
       </c>
       <c r="BA255" t="s">
@@ -46658,7 +46684,7 @@
       <c r="AY256" t="s">
         <v>23</v>
       </c>
-      <c r="AZ256" s="1">
+      <c r="AZ256" s="2">
         <v>46038</v>
       </c>
       <c r="BA256" t="s">
@@ -46777,7 +46803,7 @@
       <c r="AY257" t="s">
         <v>24</v>
       </c>
-      <c r="AZ257" s="1">
+      <c r="AZ257" s="2">
         <v>46038</v>
       </c>
       <c r="BA257" t="s">
@@ -46896,7 +46922,7 @@
       <c r="AY258" t="s">
         <v>24</v>
       </c>
-      <c r="AZ258" s="1">
+      <c r="AZ258" s="2">
         <v>46038</v>
       </c>
       <c r="BA258" t="s">
@@ -47015,7 +47041,7 @@
       <c r="AY259" t="s">
         <v>24</v>
       </c>
-      <c r="AZ259" s="1">
+      <c r="AZ259" s="2">
         <v>46038</v>
       </c>
       <c r="BA259" t="s">
@@ -47134,7 +47160,7 @@
       <c r="AY260" t="s">
         <v>24</v>
       </c>
-      <c r="AZ260" s="1">
+      <c r="AZ260" s="2">
         <v>46038</v>
       </c>
       <c r="BA260" t="s">
@@ -47253,7 +47279,7 @@
       <c r="AY261" t="s">
         <v>24</v>
       </c>
-      <c r="AZ261" s="1">
+      <c r="AZ261" s="2">
         <v>46038</v>
       </c>
       <c r="BA261" t="s">
@@ -47372,7 +47398,7 @@
       <c r="AY262" t="s">
         <v>24</v>
       </c>
-      <c r="AZ262" s="1">
+      <c r="AZ262" s="2">
         <v>46038</v>
       </c>
       <c r="BA262" t="s">
@@ -47482,7 +47508,7 @@
       <c r="AY263" t="s">
         <v>23</v>
       </c>
-      <c r="AZ263" s="1">
+      <c r="AZ263" s="2">
         <v>46045</v>
       </c>
       <c r="BA263" t="s">
@@ -47601,7 +47627,7 @@
       <c r="AY264" t="s">
         <v>24</v>
       </c>
-      <c r="AZ264" s="1">
+      <c r="AZ264" s="2">
         <v>46045</v>
       </c>
       <c r="BA264" t="s">
@@ -47720,7 +47746,7 @@
       <c r="AY265" t="s">
         <v>24</v>
       </c>
-      <c r="AZ265" s="1">
+      <c r="AZ265" s="2">
         <v>46045</v>
       </c>
       <c r="BA265" t="s">
@@ -47839,7 +47865,7 @@
       <c r="AY266" t="s">
         <v>24</v>
       </c>
-      <c r="AZ266" s="1">
+      <c r="AZ266" s="2">
         <v>46045</v>
       </c>
       <c r="BA266" t="s">
@@ -47958,7 +47984,7 @@
       <c r="AY267" t="s">
         <v>24</v>
       </c>
-      <c r="AZ267" s="1">
+      <c r="AZ267" s="2">
         <v>46045</v>
       </c>
       <c r="BA267" t="s">
@@ -48077,7 +48103,7 @@
       <c r="AY268" t="s">
         <v>24</v>
       </c>
-      <c r="AZ268" s="1">
+      <c r="AZ268" s="2">
         <v>46045</v>
       </c>
       <c r="BA268" t="s">
@@ -48196,7 +48222,7 @@
       <c r="AY269" t="s">
         <v>24</v>
       </c>
-      <c r="AZ269" s="1">
+      <c r="AZ269" s="2">
         <v>46045</v>
       </c>
       <c r="BA269" t="s">
@@ -48306,7 +48332,7 @@
       <c r="AY270" t="s">
         <v>23</v>
       </c>
-      <c r="AZ270" s="1">
+      <c r="AZ270" s="2">
         <v>46052</v>
       </c>
       <c r="BA270" t="s">
@@ -48425,7 +48451,7 @@
       <c r="AY271" t="s">
         <v>24</v>
       </c>
-      <c r="AZ271" s="1">
+      <c r="AZ271" s="2">
         <v>46052</v>
       </c>
       <c r="BA271" t="s">
@@ -48544,7 +48570,7 @@
       <c r="AY272" t="s">
         <v>24</v>
       </c>
-      <c r="AZ272" s="1">
+      <c r="AZ272" s="2">
         <v>46052</v>
       </c>
       <c r="BA272" t="s">
@@ -48663,7 +48689,7 @@
       <c r="AY273" t="s">
         <v>24</v>
       </c>
-      <c r="AZ273" s="1">
+      <c r="AZ273" s="2">
         <v>46052</v>
       </c>
       <c r="BA273" t="s">
@@ -48782,7 +48808,7 @@
       <c r="AY274" t="s">
         <v>24</v>
       </c>
-      <c r="AZ274" s="1">
+      <c r="AZ274" s="2">
         <v>46052</v>
       </c>
       <c r="BA274" t="s">
@@ -48901,7 +48927,7 @@
       <c r="AY275" t="s">
         <v>24</v>
       </c>
-      <c r="AZ275" s="1">
+      <c r="AZ275" s="2">
         <v>46052</v>
       </c>
       <c r="BA275" t="s">
@@ -49020,7 +49046,7 @@
       <c r="AY276" t="s">
         <v>24</v>
       </c>
-      <c r="AZ276" s="1">
+      <c r="AZ276" s="2">
         <v>46052</v>
       </c>
       <c r="BA276" t="s">
@@ -49130,7 +49156,7 @@
       <c r="AY277" t="s">
         <v>23</v>
       </c>
-      <c r="AZ277" s="1">
+      <c r="AZ277" s="2">
         <v>46059</v>
       </c>
       <c r="BA277" t="s">
@@ -49249,7 +49275,7 @@
       <c r="AY278" t="s">
         <v>24</v>
       </c>
-      <c r="AZ278" s="1">
+      <c r="AZ278" s="2">
         <v>46059</v>
       </c>
       <c r="BA278" t="s">
@@ -49368,7 +49394,7 @@
       <c r="AY279" t="s">
         <v>24</v>
       </c>
-      <c r="AZ279" s="1">
+      <c r="AZ279" s="2">
         <v>46059</v>
       </c>
       <c r="BA279" t="s">
@@ -49487,7 +49513,7 @@
       <c r="AY280" t="s">
         <v>24</v>
       </c>
-      <c r="AZ280" s="1">
+      <c r="AZ280" s="2">
         <v>46059</v>
       </c>
       <c r="BA280" t="s">
@@ -49606,7 +49632,7 @@
       <c r="AY281" t="s">
         <v>24</v>
       </c>
-      <c r="AZ281" s="1">
+      <c r="AZ281" s="2">
         <v>46059</v>
       </c>
       <c r="BA281" t="s">
@@ -49725,7 +49751,7 @@
       <c r="AY282" t="s">
         <v>24</v>
       </c>
-      <c r="AZ282" s="1">
+      <c r="AZ282" s="2">
         <v>46059</v>
       </c>
       <c r="BA282" t="s">
@@ -49844,7 +49870,7 @@
       <c r="AY283" t="s">
         <v>24</v>
       </c>
-      <c r="AZ283" s="1">
+      <c r="AZ283" s="2">
         <v>46059</v>
       </c>
       <c r="BA283" t="s">
@@ -49954,7 +49980,7 @@
       <c r="AY284" t="s">
         <v>23</v>
       </c>
-      <c r="AZ284" s="1">
+      <c r="AZ284" s="2">
         <v>46066</v>
       </c>
       <c r="BA284" t="s">
@@ -50073,7 +50099,7 @@
       <c r="AY285" t="s">
         <v>24</v>
       </c>
-      <c r="AZ285" s="1">
+      <c r="AZ285" s="2">
         <v>46066</v>
       </c>
       <c r="BA285" t="s">
@@ -50192,7 +50218,7 @@
       <c r="AY286" t="s">
         <v>24</v>
       </c>
-      <c r="AZ286" s="1">
+      <c r="AZ286" s="2">
         <v>46066</v>
       </c>
       <c r="BA286" t="s">
@@ -50311,7 +50337,7 @@
       <c r="AY287" t="s">
         <v>24</v>
       </c>
-      <c r="AZ287" s="1">
+      <c r="AZ287" s="2">
         <v>46066</v>
       </c>
       <c r="BA287" t="s">
@@ -50430,7 +50456,7 @@
       <c r="AY288" t="s">
         <v>24</v>
       </c>
-      <c r="AZ288" s="1">
+      <c r="AZ288" s="2">
         <v>46066</v>
       </c>
       <c r="BA288" t="s">
@@ -50549,7 +50575,7 @@
       <c r="AY289" t="s">
         <v>24</v>
       </c>
-      <c r="AZ289" s="1">
+      <c r="AZ289" s="2">
         <v>46066</v>
       </c>
       <c r="BA289" t="s">
@@ -50668,7 +50694,7 @@
       <c r="AY290" t="s">
         <v>24</v>
       </c>
-      <c r="AZ290" s="1">
+      <c r="AZ290" s="2">
         <v>46066</v>
       </c>
       <c r="BA290" t="s">
@@ -50778,7 +50804,7 @@
       <c r="AY291" t="s">
         <v>23</v>
       </c>
-      <c r="AZ291" s="1">
+      <c r="AZ291" s="2">
         <v>46073</v>
       </c>
       <c r="BA291" t="s">
@@ -50897,7 +50923,7 @@
       <c r="AY292" t="s">
         <v>24</v>
       </c>
-      <c r="AZ292" s="1">
+      <c r="AZ292" s="2">
         <v>46073</v>
       </c>
       <c r="BA292" t="s">
@@ -51016,7 +51042,7 @@
       <c r="AY293" t="s">
         <v>24</v>
       </c>
-      <c r="AZ293" s="1">
+      <c r="AZ293" s="2">
         <v>46073</v>
       </c>
       <c r="BA293" t="s">
@@ -51135,7 +51161,7 @@
       <c r="AY294" t="s">
         <v>24</v>
       </c>
-      <c r="AZ294" s="1">
+      <c r="AZ294" s="2">
         <v>46073</v>
       </c>
       <c r="BA294" t="s">
@@ -51254,7 +51280,7 @@
       <c r="AY295" t="s">
         <v>24</v>
       </c>
-      <c r="AZ295" s="1">
+      <c r="AZ295" s="2">
         <v>46073</v>
       </c>
       <c r="BA295" t="s">
@@ -51373,7 +51399,7 @@
       <c r="AY296" t="s">
         <v>24</v>
       </c>
-      <c r="AZ296" s="1">
+      <c r="AZ296" s="2">
         <v>46073</v>
       </c>
       <c r="BA296" t="s">
@@ -51492,7 +51518,7 @@
       <c r="AY297" t="s">
         <v>24</v>
       </c>
-      <c r="AZ297" s="1">
+      <c r="AZ297" s="2">
         <v>46073</v>
       </c>
       <c r="BA297" t="s">
@@ -51602,7 +51628,7 @@
       <c r="AY298" t="s">
         <v>23</v>
       </c>
-      <c r="AZ298" s="1">
+      <c r="AZ298" s="2">
         <v>46080</v>
       </c>
       <c r="BA298" t="s">
@@ -51721,7 +51747,7 @@
       <c r="AY299" t="s">
         <v>24</v>
       </c>
-      <c r="AZ299" s="1">
+      <c r="AZ299" s="2">
         <v>46080</v>
       </c>
       <c r="BA299" t="s">
@@ -51840,7 +51866,7 @@
       <c r="AY300" t="s">
         <v>24</v>
       </c>
-      <c r="AZ300" s="1">
+      <c r="AZ300" s="2">
         <v>46080</v>
       </c>
       <c r="BA300" t="s">
@@ -51959,7 +51985,7 @@
       <c r="AY301" t="s">
         <v>24</v>
       </c>
-      <c r="AZ301" s="1">
+      <c r="AZ301" s="2">
         <v>46080</v>
       </c>
       <c r="BA301" t="s">
@@ -52078,7 +52104,7 @@
       <c r="AY302" t="s">
         <v>24</v>
       </c>
-      <c r="AZ302" s="1">
+      <c r="AZ302" s="2">
         <v>46080</v>
       </c>
       <c r="BA302" t="s">
@@ -52197,7 +52223,7 @@
       <c r="AY303" t="s">
         <v>24</v>
       </c>
-      <c r="AZ303" s="1">
+      <c r="AZ303" s="2">
         <v>46080</v>
       </c>
       <c r="BA303" t="s">
@@ -52316,7 +52342,7 @@
       <c r="AY304" t="s">
         <v>24</v>
       </c>
-      <c r="AZ304" s="1">
+      <c r="AZ304" s="2">
         <v>46080</v>
       </c>
       <c r="BA304" t="s">
